--- a/USHPRR/UMo_defects_pressure_diffusion.xlsx
+++ b/USHPRR/UMo_defects_pressure_diffusion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/USHPRR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/USHPRR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2BF0BA-FAF9-A64C-90A1-232D458D4FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B14F3DF-8775-2044-A1D0-C1CB498BCD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31280" yWindow="8200" windowWidth="20200" windowHeight="16940" activeTab="8" xr2:uid="{722D8BD5-8471-1043-985F-97373411828A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26800" windowHeight="20760" xr2:uid="{722D8BD5-8471-1043-985F-97373411828A}"/>
   </bookViews>
   <sheets>
     <sheet name="u10mo" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="56">
   <si>
     <t>int0</t>
   </si>
@@ -210,6 +210,30 @@
   </si>
   <si>
     <t>fraction</t>
+  </si>
+  <si>
+    <t>int40</t>
+  </si>
+  <si>
+    <t>int-40</t>
+  </si>
+  <si>
+    <t>D_int vs P</t>
+  </si>
+  <si>
+    <t>D=A*P+B</t>
+  </si>
+  <si>
+    <t>D_vac vs P</t>
+  </si>
+  <si>
+    <t>units of cm^2/s</t>
+  </si>
+  <si>
+    <t>vac40</t>
+  </si>
+  <si>
+    <t>vac-40</t>
   </si>
 </sst>
 </file>
@@ -395,7 +419,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$12:$M$16</c:f>
+              <c:f>u10mo!$O$12:$O$16</c:f>
               <c:numCache>
                 <c:formatCode>0.0000E+00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -702,6 +726,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -709,7 +734,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1339,6 +1363,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1346,7 +1371,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1976,6 +2000,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1983,7 +2008,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2568,6 +2592,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2575,7 +2600,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3255,6 +3279,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3262,7 +3287,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3942,6 +3966,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3949,7 +3974,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4337,6 +4361,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4344,7 +4369,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4637,6 +4661,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4644,7 +4669,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4998,6 +5022,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5005,7 +5030,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5298,6 +5322,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5305,7 +5330,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5598,6 +5622,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5605,7 +5630,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5705,7 +5729,7 @@
                   <c:y val="-0.13963809812235009"/>
                 </c:manualLayout>
               </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -5737,10 +5761,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$E$4:$I$4</c:f>
+              <c:f>u10mo!$E$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5756,15 +5780,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$E$6:$I$6</c:f>
+              <c:f>u10mo!$E$6:$K$6</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1.11329795332533E-6</c:v>
                 </c:pt>
@@ -5779,6 +5809,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1.15925182693878E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.0358816941176504E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3326659102040801E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5831,11 +5867,11 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="9.9694927108077799E-2"/>
-                  <c:y val="-7.0009085402786192E-2"/>
+                  <c:x val="0.21001651975738866"/>
+                  <c:y val="-5.9518852210781348E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -5867,10 +5903,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$E$4:$I$4</c:f>
+              <c:f>u10mo!$E$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5886,15 +5922,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$E$7:$I$7</c:f>
+              <c:f>u10mo!$E$7:$K$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>8.3726084830732301E-7</c:v>
                 </c:pt>
@@ -5909,6 +5951,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9.0119544749099604E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.5323770352941203E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0432410526290499E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5945,12 +5993,62 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.1243322762296363E-2"/>
+                  <c:y val="-2.997198667474258E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$E$4:$I$4</c:f>
+              <c:f>u10mo!$E$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5966,15 +6064,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$E$8:$I$8</c:f>
+              <c:f>u10mo!$E$8:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>6.1636555289315698E-7</c:v>
                 </c:pt>
@@ -5989,6 +6093,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.5117995202881195E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.6214297704681899E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8926903130852297E-7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6037,14 +6147,50 @@
             </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.13957241562262604"/>
+                  <c:y val="-3.8025817686250754E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$E$4:$I$4</c:f>
+              <c:f>u10mo!$E$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6060,15 +6206,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$E$9:$I$9</c:f>
+              <c:f>u10mo!$E$9:$K$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>3.8045353416566599E-7</c:v>
                 </c:pt>
@@ -6083,6 +6235,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4.24116154669868E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6119212332392498E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.2093807308523396E-7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6119,12 +6277,56 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$E$4:$I$4</c:f>
+              <c:f>u10mo!$E$4:$K$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6140,15 +6342,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$E$10:$I$10</c:f>
+              <c:f>u10mo!$E$10:$K$10</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2.33486662953181E-7</c:v>
                 </c:pt>
@@ -6163,6 +6371,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2.52499794333733E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.73226103913565E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.3855813320528202E-7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6250,9 +6464,8 @@
       <c:valAx>
         <c:axId val="1140835920"/>
         <c:scaling>
-          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:max val="1.9999999999999999E-6"/>
+          <c:max val="1.5999999999999999E-6"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6273,7 +6486,7 @@
         <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -6321,6 +6534,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6328,7 +6542,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6621,6 +6834,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6628,7 +6842,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6724,11 +6937,11 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.14563673415248821"/>
-                  <c:y val="-3.5895669291338583E-2"/>
+                  <c:x val="0.14876077703150811"/>
+                  <c:y val="-9.9650590551181098E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -6760,10 +6973,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$M$4:$Q$4</c:f>
+              <c:f>u10mo!$O$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6779,15 +6992,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$6:$Q$6</c:f>
+              <c:f>u10mo!$O$6:$U$6</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2.5024402217580399E-7</c:v>
                 </c:pt>
@@ -6802,6 +7021,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2.71646397518938E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.19024020475512E-7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.16900458245706E-7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6890,10 +7115,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$M$4:$Q$4</c:f>
+              <c:f>u10mo!$O$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6909,15 +7134,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$7:$Q$7</c:f>
+              <c:f>u10mo!$O$7:$U$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1.4339706186604699E-7</c:v>
                 </c:pt>
@@ -6970,10 +7201,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$M$4:$Q$4</c:f>
+              <c:f>u10mo!$O$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6989,15 +7220,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$8:$Q$8</c:f>
+              <c:f>u10mo!$O$8:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>7.5766970436510902E-8</c:v>
                 </c:pt>
@@ -7048,12 +7285,56 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$M$4:$Q$4</c:f>
+              <c:f>u10mo!$O$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7069,15 +7350,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$9:$Q$9</c:f>
+              <c:f>u10mo!$O$9:$U$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>2.75642803570089E-8</c:v>
                 </c:pt>
@@ -7092,6 +7379,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3.16526050011251E-8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3654310194907999E-8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4228405073876897E-8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7128,12 +7421,56 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>u10mo!$M$4:$Q$4</c:f>
+              <c:f>u10mo!$O$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7149,15 +7486,21 @@
                 <c:pt idx="4">
                   <c:v>-10</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-40</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>u10mo!$M$10:$Q$10</c:f>
+              <c:f>u10mo!$O$10:$U$10</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>9.0627559161478905E-9</c:v>
                 </c:pt>
@@ -7172,6 +7515,12 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>6.6495730285757098E-9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9870609235288698E-9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.3725787902197404E-9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7282,7 +7631,7 @@
         <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -7330,6 +7679,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7337,7 +7687,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7800,6 +8149,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7807,7 +8157,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8291,6 +8640,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8298,7 +8648,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8755,6 +9104,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8762,7 +9112,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9584,6 +9933,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9591,7 +9941,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10368,6 +10717,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10375,7 +10725,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11080,6 +11429,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11087,7 +11437,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -22246,16 +22595,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>412750</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22282,16 +22631,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22320,16 +22669,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -23311,10 +23660,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FDE3FAC-5150-1240-AFA1-6C4775590509}">
-  <dimension ref="A1:AH87"/>
+  <dimension ref="A1:AT87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="23" max="23" width="12.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="E1" t="s">
         <v>0</v>
       </c>
@@ -23330,26 +23682,32 @@
       <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>10</v>
       </c>
+      <c r="W1" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -23358,26 +23716,47 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
       <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="V2" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" s="2" cm="1">
+        <f t="array" ref="W2:X2">LINEST(E12:K12,E4:K4)</f>
+        <v>-2.5011728441407408E-7</v>
+      </c>
+      <c r="X2" s="2">
+        <v>5.0616276743388769E-5</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
+      <c r="M3" s="1"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="1"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="2" cm="1">
+        <f t="array" ref="W3:X3">LINEST(O12:U12,O4:U4)</f>
+        <v>-5.462137287825837E-8</v>
+      </c>
+      <c r="X3" s="2">
+        <v>1.1895618575832038E-5</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D4" t="s">
         <v>12</v>
       </c>
@@ -23396,37 +23775,49 @@
       <c r="I4">
         <v>-10</v>
       </c>
-      <c r="L4" t="s">
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>-40</v>
+      </c>
+      <c r="N4" t="s">
         <v>12</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>0</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>5</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>-5</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>-10</v>
       </c>
+      <c r="T4">
+        <v>40</v>
+      </c>
+      <c r="U4">
+        <v>-40</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C6">
         <f>1/((0.000086173)*D6)</f>
         <v>9.670469095114866</v>
@@ -23449,31 +23840,44 @@
       <c r="I6" s="1">
         <v>1.15925182693878E-6</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6">
+      <c r="J6" s="1">
+        <v>9.0358816941176504E-7</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.3326659102040801E-6</v>
+      </c>
+      <c r="M6">
         <v>1200</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>1200</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>2.5024402217580399E-7</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>2.52651821219531E-7</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>2.53342456378159E-7</v>
       </c>
-      <c r="P6" s="1">
+      <c r="R6" s="1">
         <v>2.5728060049426198E-7</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="S6" s="1">
         <v>2.71646397518938E-7</v>
       </c>
-      <c r="R6" s="1"/>
+      <c r="T6" s="1">
+        <v>2.19024020475512E-7</v>
+      </c>
+      <c r="U6" s="1">
+        <v>3.16900458245706E-7</v>
+      </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -23502,28 +23906,37 @@
       <c r="I7" s="1">
         <v>9.0119544749099604E-7</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="L7">
+      <c r="J7" s="1">
+        <v>6.5323770352941203E-7</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.0432410526290499E-6</v>
+      </c>
+      <c r="N7">
         <v>1100</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>1.4339706186604699E-7</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>1.43843291266782E-7</v>
       </c>
-      <c r="O7" s="1">
+      <c r="Q7" s="1">
         <v>1.3767151154728899E-7</v>
       </c>
-      <c r="P7" s="1">
+      <c r="R7" s="1">
         <v>1.54890222621316E-7</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="S7" s="1">
         <v>1.4975911524563101E-7</v>
       </c>
-      <c r="R7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -23553,28 +23966,37 @@
       <c r="I8" s="1">
         <v>6.5117995202881195E-7</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="L8">
+      <c r="J8" s="1">
+        <v>4.6214297704681899E-7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>7.8926903130852297E-7</v>
+      </c>
+      <c r="N8">
         <v>1000</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
         <v>7.5766970436510902E-8</v>
       </c>
-      <c r="N8" s="1">
+      <c r="P8" s="1">
         <v>6.4400101777887004E-8</v>
       </c>
-      <c r="O8" s="1">
+      <c r="Q8" s="1">
         <v>6.4093417879696994E-8</v>
       </c>
-      <c r="P8" s="1">
+      <c r="R8" s="1">
         <v>6.6530254183604604E-8</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="S8" s="1">
         <v>6.8396062658816495E-8</v>
       </c>
-      <c r="R8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -23604,28 +24026,41 @@
       <c r="I9" s="1">
         <v>4.24116154669868E-7</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="L9">
+      <c r="J9" s="1">
+        <v>2.6119212332392498E-7</v>
+      </c>
+      <c r="K9" s="1">
+        <v>5.2093807308523396E-7</v>
+      </c>
+      <c r="N9">
         <v>900</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>2.75642803570089E-8</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>2.61388441701042E-8</v>
       </c>
-      <c r="O9" s="1">
+      <c r="Q9" s="1">
         <v>2.0284068832220799E-8</v>
       </c>
-      <c r="P9" s="1">
+      <c r="R9" s="1">
         <v>2.9048263897847401E-8</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="S9" s="1">
         <v>3.16526050011251E-8</v>
       </c>
-      <c r="R9" s="1"/>
+      <c r="T9" s="1">
+        <v>2.3654310194907999E-8</v>
+      </c>
+      <c r="U9" s="1">
+        <v>3.4228405073876897E-8</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10">
         <f t="shared" si="0"/>
         <v>14.5057036426723</v>
@@ -23648,28 +24083,41 @@
       <c r="I10" s="1">
         <v>2.52499794333733E-7</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="L10">
+      <c r="J10" s="1">
+        <v>1.73226103913565E-7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.3855813320528202E-7</v>
+      </c>
+      <c r="N10">
         <v>800</v>
       </c>
-      <c r="M10" s="1">
+      <c r="O10" s="1">
         <v>9.0627559161478905E-9</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>6.4151084969624403E-9</v>
       </c>
-      <c r="O10" s="1">
+      <c r="Q10" s="1">
         <v>1.18659055456386E-8</v>
       </c>
-      <c r="P10" s="1">
+      <c r="R10" s="1">
         <v>1.09261694877372E-8</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="S10" s="1">
         <v>6.6495730285757098E-9</v>
       </c>
-      <c r="R10" s="1"/>
+      <c r="T10" s="1">
+        <v>7.9870609235288698E-9</v>
+      </c>
+      <c r="U10" s="1">
+        <v>8.3725787902197404E-9</v>
+      </c>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
         <v>19</v>
       </c>
@@ -23679,17 +24127,21 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12">
         <f>1/((0.000086173)*D12)</f>
         <v>9.670469095114866</v>
@@ -23702,7 +24154,7 @@
         <v>5.092410388168946E-5</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" ref="E12:I16" si="1">F6*5489*$B$9/6</f>
+        <f t="shared" ref="E12:K16" si="1">F6*5489*$B$9/6</f>
         <v>4.9297734296438011E-5</v>
       </c>
       <c r="G12" s="2">
@@ -23717,33 +24169,50 @@
         <f t="shared" si="1"/>
         <v>5.3026110650558022E-5</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="L12">
+      <c r="J12" s="2">
+        <f t="shared" si="1"/>
+        <v>4.1331628849176482E-5</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="1"/>
+        <v>6.0958359842584964E-5</v>
+      </c>
+      <c r="N12">
         <v>1200</v>
       </c>
-      <c r="M12" s="2">
-        <f>M6*5487*$B$9/6</f>
+      <c r="O12" s="2">
+        <f>O6*5487*$B$9/6</f>
         <v>1.1442407913988637E-5</v>
       </c>
-      <c r="N12" s="2">
-        <f t="shared" ref="N12:Q12" si="2">N6*5487*$B$9/6</f>
+      <c r="P12" s="2">
+        <f t="shared" ref="P12:U12" si="2">P6*5487*$B$9/6</f>
         <v>1.1552504525263053E-5</v>
       </c>
-      <c r="O12" s="2">
+      <c r="Q12" s="2">
         <f t="shared" si="2"/>
         <v>1.1584083817891319E-5</v>
       </c>
-      <c r="P12" s="2">
+      <c r="R12" s="2">
         <f t="shared" si="2"/>
         <v>1.1764155457600128E-5</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="S12" s="2">
         <f t="shared" si="2"/>
         <v>1.2421031526553439E-5</v>
       </c>
-      <c r="R12" s="1"/>
+      <c r="T12" s="2">
+        <f t="shared" si="2"/>
+        <v>1.0014873336242785E-5</v>
+      </c>
+      <c r="U12" s="2">
+        <f t="shared" si="2"/>
+        <v>1.4490273453284905E-5</v>
+      </c>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13">
         <f t="shared" ref="C13:C16" si="3">1/((0.000086173)*D13)</f>
         <v>10.549602649216217</v>
@@ -23771,33 +24240,44 @@
         <f t="shared" si="1"/>
         <v>4.1222181760650638E-5</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="L13">
+      <c r="J13" s="2">
+        <f t="shared" ref="J13:K13" si="4">J7*5489*$B$9/6</f>
+        <v>2.9880181288941184E-5</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="4"/>
+        <v>4.7719584482340451E-5</v>
+      </c>
+      <c r="N13">
         <v>1100</v>
       </c>
-      <c r="M13" s="2">
-        <f t="shared" ref="M13:Q16" si="4">M7*5487*$B$9/6</f>
+      <c r="O13" s="2">
+        <f t="shared" ref="O13:S16" si="5">O7*5487*$B$9/6</f>
         <v>6.5568306538249988E-6</v>
       </c>
-      <c r="N13" s="2">
-        <f t="shared" si="4"/>
+      <c r="P13" s="2">
+        <f t="shared" si="5"/>
         <v>6.5772344931736062E-6</v>
       </c>
-      <c r="O13" s="2">
-        <f t="shared" si="4"/>
+      <c r="Q13" s="2">
+        <f t="shared" si="5"/>
         <v>6.2950298654997885E-6</v>
       </c>
-      <c r="P13" s="2">
-        <f t="shared" si="4"/>
+      <c r="R13" s="2">
+        <f t="shared" si="5"/>
         <v>7.0823554293596741E-6</v>
       </c>
-      <c r="Q13" s="2">
-        <f t="shared" si="4"/>
+      <c r="S13" s="2">
+        <f t="shared" si="5"/>
         <v>6.847735544606478E-6</v>
       </c>
-      <c r="R13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14">
         <f t="shared" si="3"/>
         <v>11.604562914137839</v>
@@ -23825,33 +24305,44 @@
         <f t="shared" si="1"/>
         <v>2.9786056305717903E-5</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="L14">
+      <c r="J14" s="2">
+        <f t="shared" ref="J14:K14" si="6">J8*5489*$B$9/6</f>
+        <v>2.1139190008416579E-5</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="6"/>
+        <v>3.6102480940437351E-5</v>
+      </c>
+      <c r="N14">
         <v>1000</v>
       </c>
-      <c r="M14" s="2">
-        <f t="shared" si="4"/>
+      <c r="O14" s="2">
+        <f t="shared" si="5"/>
         <v>3.4644447232094606E-6</v>
       </c>
-      <c r="N14" s="2">
-        <f t="shared" si="4"/>
+      <c r="P14" s="2">
+        <f t="shared" si="5"/>
         <v>2.9446946537938828E-6</v>
       </c>
-      <c r="O14" s="2">
-        <f t="shared" si="4"/>
+      <c r="Q14" s="2">
+        <f t="shared" si="5"/>
         <v>2.9306715325491448E-6</v>
       </c>
-      <c r="P14" s="2">
-        <f t="shared" si="4"/>
+      <c r="R14" s="2">
+        <f t="shared" si="5"/>
         <v>3.0420958725453197E-6</v>
       </c>
-      <c r="Q14" s="2">
-        <f t="shared" si="4"/>
+      <c r="S14" s="2">
+        <f t="shared" si="5"/>
         <v>3.1274099650743838E-6</v>
       </c>
-      <c r="R14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15">
         <f t="shared" si="3"/>
         <v>12.893958793486487</v>
@@ -23879,33 +24370,44 @@
         <f t="shared" si="1"/>
         <v>1.9399779774857544E-5</v>
       </c>
-      <c r="J15" s="1"/>
-      <c r="L15">
+      <c r="J15" s="2">
+        <f t="shared" ref="J15:K15" si="7">J9*5489*$B$9/6</f>
+        <v>1.1947363041041867E-5</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="7"/>
+        <v>2.3828575693040412E-5</v>
+      </c>
+      <c r="N15">
         <v>900</v>
       </c>
-      <c r="M15" s="2">
-        <f t="shared" si="4"/>
+      <c r="O15" s="2">
+        <f t="shared" si="5"/>
         <v>1.2603767193242319E-6</v>
       </c>
-      <c r="N15" s="2">
-        <f t="shared" si="4"/>
+      <c r="P15" s="2">
+        <f t="shared" si="5"/>
         <v>1.1951986496780146E-6</v>
       </c>
-      <c r="O15" s="2">
-        <f t="shared" si="4"/>
+      <c r="Q15" s="2">
+        <f t="shared" si="5"/>
         <v>9.2748904735329595E-7</v>
       </c>
-      <c r="P15" s="2">
-        <f t="shared" si="4"/>
+      <c r="R15" s="2">
+        <f t="shared" si="5"/>
         <v>1.3282318667290722E-6</v>
       </c>
-      <c r="Q15" s="2">
-        <f t="shared" si="4"/>
+      <c r="S15" s="2">
+        <f t="shared" si="5"/>
         <v>1.4473153636764452E-6</v>
       </c>
-      <c r="R15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C16">
         <f t="shared" si="3"/>
         <v>14.5057036426723</v>
@@ -23933,33 +24435,44 @@
         <f t="shared" si="1"/>
         <v>1.1549761425815505E-5</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="L16">
+      <c r="J16" s="2">
+        <f t="shared" ref="J16:K16" si="8">J10*5489*$B$9/6</f>
+        <v>7.9236507031796511E-6</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="8"/>
+        <v>1.5486213276364939E-5</v>
+      </c>
+      <c r="N16">
         <v>800</v>
       </c>
-      <c r="M16" s="2">
-        <f t="shared" si="4"/>
+      <c r="O16" s="2">
+        <f t="shared" si="5"/>
         <v>4.1439451426586226E-7</v>
       </c>
-      <c r="N16" s="2">
-        <f t="shared" si="4"/>
+      <c r="P16" s="2">
+        <f t="shared" si="5"/>
         <v>2.9333083602360756E-7</v>
       </c>
-      <c r="O16" s="2">
-        <f t="shared" si="4"/>
+      <c r="Q16" s="2">
+        <f t="shared" si="5"/>
         <v>5.425685310743249E-7</v>
       </c>
-      <c r="P16" s="2">
-        <f t="shared" si="4"/>
+      <c r="R16" s="2">
+        <f t="shared" si="5"/>
         <v>4.9959909982678342E-7</v>
       </c>
-      <c r="Q16" s="2">
-        <f t="shared" si="4"/>
+      <c r="S16" s="2">
+        <f t="shared" si="5"/>
         <v>3.0405172673162427E-7</v>
       </c>
-      <c r="R16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
     </row>
-    <row r="17" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:46" x14ac:dyDescent="0.2">
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23972,8 +24485,14 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
     </row>
-    <row r="18" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:46" x14ac:dyDescent="0.2">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -23986,8 +24505,14 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
     </row>
-    <row r="19" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -24014,31 +24539,49 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="1"/>
-      <c r="T19" t="s">
+      <c r="S19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T19" s="2"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Z19" t="s">
         <v>5</v>
       </c>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2" t="s">
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC19" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="AD19" s="2"/>
       <c r="AE19" s="2"/>
-      <c r="AF19" s="2" t="s">
+      <c r="AF19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="2"/>
+      <c r="AL19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="1"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="1"/>
+      <c r="AO19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="20" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D20">
         <v>1</v>
       </c>
@@ -24084,53 +24627,89 @@
       <c r="R20" s="1">
         <v>0.99936992826065696</v>
       </c>
-      <c r="T20">
+      <c r="S20">
         <v>1</v>
       </c>
-      <c r="U20" s="2">
-        <v>2.5238537299182502E-7</v>
-      </c>
-      <c r="V20" s="2">
-        <v>0.99795483093344695</v>
-      </c>
-      <c r="W20">
+      <c r="T20" s="2">
+        <v>8.7368797983193301E-7</v>
+      </c>
+      <c r="U20" s="1">
+        <v>0.99908238080205203</v>
+      </c>
+      <c r="V20" s="1">
         <v>1</v>
       </c>
-      <c r="X20" s="2">
-        <v>2.13684304612615E-7</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>0.99643077677401004</v>
+      <c r="W20" s="1">
+        <v>1.2985732484993999E-6</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0.99945226514268803</v>
       </c>
       <c r="Z20">
         <v>1</v>
       </c>
-      <c r="AA20" s="1">
-        <v>2.3503554251856299E-7</v>
-      </c>
-      <c r="AB20">
-        <v>0.99740401483132601</v>
+      <c r="AA20" s="2">
+        <v>2.5238537299182502E-7</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>0.99795483093344695</v>
       </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AD20" s="2">
-        <v>2.5800585552388799E-7</v>
+        <v>2.13684304612615E-7</v>
       </c>
       <c r="AE20" s="2">
-        <v>0.99858721293156105</v>
+        <v>0.99643077677401004</v>
       </c>
       <c r="AF20">
         <v>1</v>
       </c>
-      <c r="AG20" s="2">
+      <c r="AG20" s="1">
+        <v>2.3503554251856299E-7</v>
+      </c>
+      <c r="AH20">
+        <v>0.99740401483132601</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="2">
+        <v>2.5800585552388799E-7</v>
+      </c>
+      <c r="AK20" s="2">
+        <v>0.99858721293156105</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="2">
         <v>2.8196485872646798E-7</v>
       </c>
-      <c r="AH20" s="1">
+      <c r="AN20" s="1">
         <v>0.99859944707779302</v>
       </c>
+      <c r="AO20">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="1">
+        <v>2.02177301575039E-7</v>
+      </c>
+      <c r="AQ20">
+        <v>0.996841936743735</v>
+      </c>
+      <c r="AR20">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="1">
+        <v>3.1105540609765299E-7</v>
+      </c>
+      <c r="AT20">
+        <v>0.99883589635843895</v>
+      </c>
     </row>
-    <row r="21" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D21">
         <v>2</v>
       </c>
@@ -24176,53 +24755,89 @@
       <c r="R21" s="1">
         <v>0.99692421150991894</v>
       </c>
-      <c r="T21">
+      <c r="S21">
         <v>2</v>
       </c>
+      <c r="T21" s="2">
+        <v>9.90632068667467E-7</v>
+      </c>
       <c r="U21" s="1">
-        <v>2.6718607228680699E-7</v>
-      </c>
-      <c r="V21">
-        <v>0.99576003385759904</v>
-      </c>
-      <c r="W21">
+        <v>0.99800553165919004</v>
+      </c>
+      <c r="V21" s="1">
         <v>2</v>
       </c>
+      <c r="W21" s="1">
+        <v>1.34142357262905E-6</v>
+      </c>
       <c r="X21" s="1">
-        <v>2.4859933276081902E-7</v>
-      </c>
-      <c r="Y21">
-        <v>0.998441697567651</v>
+        <v>0.998869002032024</v>
       </c>
       <c r="Z21">
         <v>2</v>
       </c>
       <c r="AA21" s="1">
-        <v>2.4672843945098601E-7</v>
+        <v>2.6718607228680699E-7</v>
       </c>
       <c r="AB21">
-        <v>0.99861935221176301</v>
+        <v>0.99576003385759904</v>
       </c>
       <c r="AC21">
         <v>2</v>
       </c>
       <c r="AD21" s="1">
-        <v>2.6093911719792998E-7</v>
+        <v>2.4859933276081902E-7</v>
       </c>
       <c r="AE21">
-        <v>0.99693921382265605</v>
+        <v>0.998441697567651</v>
       </c>
       <c r="AF21">
         <v>2</v>
       </c>
       <c r="AG21" s="1">
+        <v>2.4672843945098601E-7</v>
+      </c>
+      <c r="AH21">
+        <v>0.99861935221176301</v>
+      </c>
+      <c r="AI21">
+        <v>2</v>
+      </c>
+      <c r="AJ21" s="1">
+        <v>2.6093911719792998E-7</v>
+      </c>
+      <c r="AK21">
+        <v>0.99693921382265605</v>
+      </c>
+      <c r="AL21">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="1">
         <v>2.9029403347333599E-7</v>
       </c>
-      <c r="AH21">
+      <c r="AN21">
         <v>0.99887920621340698</v>
       </c>
+      <c r="AO21">
+        <v>2</v>
+      </c>
+      <c r="AP21" s="1">
+        <v>2.4091665043876099E-7</v>
+      </c>
+      <c r="AQ21">
+        <v>0.99633416807278696</v>
+      </c>
+      <c r="AR21">
+        <v>2</v>
+      </c>
+      <c r="AS21" s="1">
+        <v>3.2632495721893002E-7</v>
+      </c>
+      <c r="AT21">
+        <v>0.99517840022562198</v>
+      </c>
     </row>
-    <row r="22" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D22">
         <v>3</v>
       </c>
@@ -24268,53 +24883,89 @@
       <c r="R22" s="1">
         <v>0.99790388257832596</v>
       </c>
-      <c r="T22">
+      <c r="S22">
         <v>3</v>
       </c>
+      <c r="T22" s="2">
+        <v>9.8737904585834292E-7</v>
+      </c>
       <c r="U22" s="1">
-        <v>2.4230899793744802E-7</v>
-      </c>
-      <c r="V22">
-        <v>0.99830962362306497</v>
-      </c>
-      <c r="W22">
+        <v>0.99916977191638701</v>
+      </c>
+      <c r="V22" s="1">
         <v>3</v>
       </c>
+      <c r="W22" s="1">
+        <v>1.2945566521008401E-6</v>
+      </c>
       <c r="X22" s="1">
-        <v>2.5923707331433298E-7</v>
-      </c>
-      <c r="Y22">
-        <v>0.99795013471120897</v>
+        <v>0.998716214514343</v>
       </c>
       <c r="Z22">
         <v>3</v>
       </c>
       <c r="AA22" s="1">
-        <v>2.56495149666242E-7</v>
+        <v>2.4230899793744802E-7</v>
       </c>
       <c r="AB22">
-        <v>0.99832253999722298</v>
+        <v>0.99830962362306497</v>
       </c>
       <c r="AC22">
         <v>3</v>
       </c>
       <c r="AD22" s="1">
-        <v>2.4610440515262798E-7</v>
+        <v>2.5923707331433298E-7</v>
       </c>
       <c r="AE22">
-        <v>0.99675488049164496</v>
+        <v>0.99795013471120897</v>
       </c>
       <c r="AF22">
         <v>3</v>
       </c>
       <c r="AG22" s="1">
+        <v>2.56495149666242E-7</v>
+      </c>
+      <c r="AH22">
+        <v>0.99832253999722298</v>
+      </c>
+      <c r="AI22">
+        <v>3</v>
+      </c>
+      <c r="AJ22" s="1">
+        <v>2.4610440515262798E-7</v>
+      </c>
+      <c r="AK22">
+        <v>0.99675488049164496</v>
+      </c>
+      <c r="AL22">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="1">
         <v>2.99774554256357E-7</v>
       </c>
-      <c r="AH22">
+      <c r="AN22">
         <v>0.998616004045079</v>
       </c>
+      <c r="AO22">
+        <v>3</v>
+      </c>
+      <c r="AP22" s="1">
+        <v>2.2097067440935999E-7</v>
+      </c>
+      <c r="AQ22">
+        <v>0.99569151775194398</v>
+      </c>
+      <c r="AR22">
+        <v>3</v>
+      </c>
+      <c r="AS22" s="1">
+        <v>3.2361163130578298E-7</v>
+      </c>
+      <c r="AT22">
+        <v>0.99881807224501695</v>
+      </c>
     </row>
-    <row r="23" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D23">
         <v>4</v>
       </c>
@@ -24360,53 +25011,89 @@
       <c r="R23" s="1">
         <v>0.99957613708275295</v>
       </c>
-      <c r="T23">
+      <c r="S23">
         <v>4</v>
       </c>
+      <c r="T23" s="2">
+        <v>9.1076866650660297E-7</v>
+      </c>
       <c r="U23" s="1">
-        <v>2.5157294431110801E-7</v>
-      </c>
-      <c r="V23">
-        <v>0.99709767583356002</v>
-      </c>
-      <c r="W23">
+        <v>0.99647760656148598</v>
+      </c>
+      <c r="V23" s="1">
         <v>4</v>
       </c>
+      <c r="W23" s="1">
+        <v>1.48291640240096E-6</v>
+      </c>
       <c r="X23" s="1">
-        <v>2.7177201920048102E-7</v>
-      </c>
-      <c r="Y23">
-        <v>0.99852966459472403</v>
+        <v>0.99522757337178402</v>
       </c>
       <c r="Z23">
         <v>4</v>
       </c>
       <c r="AA23" s="1">
-        <v>2.6446708496212402E-7</v>
+        <v>2.5157294431110801E-7</v>
       </c>
       <c r="AB23">
-        <v>0.99936761828785403</v>
+        <v>0.99709767583356002</v>
       </c>
       <c r="AC23">
         <v>4</v>
       </c>
       <c r="AD23" s="1">
-        <v>2.8435997499437401E-7</v>
+        <v>2.7177201920048102E-7</v>
       </c>
       <c r="AE23">
-        <v>0.99694235513038598</v>
+        <v>0.99852966459472403</v>
       </c>
       <c r="AF23">
         <v>4</v>
       </c>
       <c r="AG23" s="1">
+        <v>2.6446708496212402E-7</v>
+      </c>
+      <c r="AH23">
+        <v>0.99936761828785403</v>
+      </c>
+      <c r="AI23">
+        <v>4</v>
+      </c>
+      <c r="AJ23" s="1">
+        <v>2.8435997499437401E-7</v>
+      </c>
+      <c r="AK23">
+        <v>0.99694235513038598</v>
+      </c>
+      <c r="AL23">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="1">
         <v>2.6113207659941501E-7</v>
       </c>
-      <c r="AH23">
+      <c r="AN23">
         <v>0.99580782100693599</v>
       </c>
+      <c r="AO23">
+        <v>4</v>
+      </c>
+      <c r="AP23" s="1">
+        <v>2.3619828168454201E-7</v>
+      </c>
+      <c r="AQ23">
+        <v>0.99709261143803396</v>
+      </c>
+      <c r="AR23">
+        <v>4</v>
+      </c>
+      <c r="AS23" s="1">
+        <v>3.3233005086627201E-7</v>
+      </c>
+      <c r="AT23">
+        <v>0.99725345840322899</v>
+      </c>
     </row>
-    <row r="24" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D24">
         <v>5</v>
       </c>
@@ -24452,53 +25139,89 @@
       <c r="R24" s="1">
         <v>0.99888520129501301</v>
       </c>
-      <c r="T24">
+      <c r="S24">
         <v>5</v>
       </c>
+      <c r="T24" s="2">
+        <v>8.32163074669868E-7</v>
+      </c>
       <c r="U24" s="1">
-        <v>2.1689550535513401E-7</v>
-      </c>
-      <c r="V24">
-        <v>0.99707302000289999</v>
-      </c>
-      <c r="W24">
+        <v>0.99823267774834601</v>
+      </c>
+      <c r="V24" s="1">
         <v>5</v>
       </c>
+      <c r="W24" s="1">
+        <v>1.3200610986794699E-6</v>
+      </c>
       <c r="X24" s="1">
-        <v>2.7775282874821898E-7</v>
-      </c>
-      <c r="Y24">
-        <v>0.998979822499519</v>
+        <v>0.99943952945960501</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24" s="1">
-        <v>2.6093605352133801E-7</v>
+        <v>2.1689550535513401E-7</v>
       </c>
       <c r="AB24">
-        <v>0.99796398140319598</v>
+        <v>0.99707302000289999</v>
       </c>
       <c r="AC24">
         <v>5</v>
       </c>
       <c r="AD24" s="1">
-        <v>2.5760113968349199E-7</v>
+        <v>2.7775282874821898E-7</v>
       </c>
       <c r="AE24">
-        <v>0.99783821097598402</v>
+        <v>0.998979822499519</v>
       </c>
       <c r="AF24">
         <v>5</v>
       </c>
       <c r="AG24" s="1">
+        <v>2.6093605352133801E-7</v>
+      </c>
+      <c r="AH24">
+        <v>0.99796398140319598</v>
+      </c>
+      <c r="AI24">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="1">
+        <v>2.5760113968349199E-7</v>
+      </c>
+      <c r="AK24">
+        <v>0.99783821097598402</v>
+      </c>
+      <c r="AL24">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="1">
         <v>2.83856769766745E-7</v>
       </c>
-      <c r="AH24">
+      <c r="AN24">
         <v>0.99926745387215499</v>
       </c>
+      <c r="AO24">
+        <v>5</v>
+      </c>
+      <c r="AP24" s="1">
+        <v>1.8276667941198501E-7</v>
+      </c>
+      <c r="AQ24">
+        <v>0.99486270913913399</v>
+      </c>
+      <c r="AR24">
+        <v>5</v>
+      </c>
+      <c r="AS24" s="1">
+        <v>3.1594666697667499E-7</v>
+      </c>
+      <c r="AT24">
+        <v>0.99913986548836198</v>
+      </c>
     </row>
-    <row r="25" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D25">
         <v>6</v>
       </c>
@@ -24544,53 +25267,89 @@
       <c r="R25" s="1">
         <v>0.999490823468975</v>
       </c>
-      <c r="T25">
+      <c r="S25">
         <v>6</v>
       </c>
+      <c r="T25" s="1">
+        <v>8.5474513229291699E-7</v>
+      </c>
       <c r="U25" s="1">
-        <v>2.50360085314633E-7</v>
-      </c>
-      <c r="V25">
-        <v>0.99799307757498401</v>
-      </c>
-      <c r="W25">
+        <v>0.99719842818456705</v>
+      </c>
+      <c r="V25" s="1">
         <v>6</v>
       </c>
+      <c r="W25" s="1">
+        <v>1.2825481978391399E-6</v>
+      </c>
       <c r="X25" s="1">
-        <v>2.4284643476336898E-7</v>
-      </c>
-      <c r="Y25">
-        <v>0.99713896906228505</v>
+        <v>0.99941956768688001</v>
       </c>
       <c r="Z25">
         <v>6</v>
       </c>
       <c r="AA25" s="1">
-        <v>2.3583815354383901E-7</v>
+        <v>2.50360085314633E-7</v>
       </c>
       <c r="AB25">
-        <v>0.99789581167823604</v>
+        <v>0.99799307757498401</v>
       </c>
       <c r="AC25">
         <v>6</v>
       </c>
       <c r="AD25" s="1">
-        <v>2.5539864151353799E-7</v>
+        <v>2.4284643476336898E-7</v>
       </c>
       <c r="AE25">
-        <v>0.99919252673947201</v>
+        <v>0.99713896906228505</v>
       </c>
       <c r="AF25">
         <v>6</v>
       </c>
       <c r="AG25" s="1">
+        <v>2.3583815354383901E-7</v>
+      </c>
+      <c r="AH25">
+        <v>0.99789581167823604</v>
+      </c>
+      <c r="AI25">
+        <v>6</v>
+      </c>
+      <c r="AJ25" s="1">
+        <v>2.5539864151353799E-7</v>
+      </c>
+      <c r="AK25">
+        <v>0.99919252673947201</v>
+      </c>
+      <c r="AL25">
+        <v>6</v>
+      </c>
+      <c r="AM25" s="1">
         <v>2.7308773018075502E-7</v>
       </c>
-      <c r="AH25">
+      <c r="AN25">
         <v>0.99904943808132296</v>
       </c>
+      <c r="AO25">
+        <v>6</v>
+      </c>
+      <c r="AP25" s="1">
+        <v>2.5432188386709701E-7</v>
+      </c>
+      <c r="AQ25">
+        <v>0.99857985839040198</v>
+      </c>
+      <c r="AR25">
+        <v>6</v>
+      </c>
+      <c r="AS25" s="1">
+        <v>3.2925327947198698E-7</v>
+      </c>
+      <c r="AT25">
+        <v>0.998770753810033</v>
+      </c>
     </row>
-    <row r="26" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D26">
         <v>7</v>
       </c>
@@ -24636,53 +25395,89 @@
       <c r="R26" s="3">
         <v>0.99905962723082098</v>
       </c>
-      <c r="T26">
+      <c r="S26">
         <v>7</v>
       </c>
-      <c r="U26" s="1">
-        <v>2.67956915450386E-7</v>
-      </c>
-      <c r="V26">
-        <v>0.99670752480722902</v>
-      </c>
-      <c r="W26">
+      <c r="T26" s="1">
+        <v>9.4146610996398596E-7</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0.99943597272530305</v>
+      </c>
+      <c r="V26" s="3">
         <v>7</v>
       </c>
-      <c r="X26" s="1">
-        <v>2.42028565926648E-7</v>
-      </c>
-      <c r="Y26">
-        <v>0.99672445576192004</v>
+      <c r="W26" s="3">
+        <v>1.30732379687875E-6</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0.99959173914981103</v>
       </c>
       <c r="Z26">
         <v>7</v>
       </c>
       <c r="AA26" s="1">
-        <v>2.5412430201004998E-7</v>
+        <v>2.67956915450386E-7</v>
       </c>
       <c r="AB26">
-        <v>0.99798081099289104</v>
+        <v>0.99670752480722902</v>
       </c>
       <c r="AC26">
         <v>7</v>
       </c>
       <c r="AD26" s="1">
-        <v>2.5503956761419E-7</v>
+        <v>2.42028565926648E-7</v>
       </c>
       <c r="AE26">
-        <v>0.99770035494442799</v>
+        <v>0.99672445576192004</v>
       </c>
       <c r="AF26">
         <v>7</v>
       </c>
       <c r="AG26" s="1">
+        <v>2.5412430201004998E-7</v>
+      </c>
+      <c r="AH26">
+        <v>0.99798081099289104</v>
+      </c>
+      <c r="AI26">
+        <v>7</v>
+      </c>
+      <c r="AJ26" s="1">
+        <v>2.5503956761419E-7</v>
+      </c>
+      <c r="AK26">
+        <v>0.99770035494442799</v>
+      </c>
+      <c r="AL26">
+        <v>7</v>
+      </c>
+      <c r="AM26" s="1">
         <v>2.6171034401110001E-7</v>
       </c>
-      <c r="AH26">
+      <c r="AN26">
         <v>0.99843706088351403</v>
       </c>
+      <c r="AO26">
+        <v>7</v>
+      </c>
+      <c r="AP26" s="1">
+        <v>2.2271047524188099E-7</v>
+      </c>
+      <c r="AQ26">
+        <v>0.99658579806957404</v>
+      </c>
+      <c r="AR26">
+        <v>7</v>
+      </c>
+      <c r="AS26" s="1">
+        <v>2.9919176120903101E-7</v>
+      </c>
+      <c r="AT26">
+        <v>0.99567854242162401</v>
+      </c>
     </row>
-    <row r="27" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D27">
         <v>8</v>
       </c>
@@ -24728,53 +25523,89 @@
       <c r="R27">
         <v>0.99953565221093799</v>
       </c>
-      <c r="T27">
+      <c r="S27">
         <v>8</v>
       </c>
-      <c r="U27" s="1">
-        <v>2.4174717230930802E-7</v>
+      <c r="T27" s="1">
+        <v>8.27126676590635E-7</v>
+      </c>
+      <c r="U27">
+        <v>0.99865406651710098</v>
       </c>
       <c r="V27">
-        <v>0.99715380777201901</v>
-      </c>
-      <c r="W27">
         <v>8</v>
       </c>
-      <c r="X27" s="1">
-        <v>2.5983967192679899E-7</v>
-      </c>
-      <c r="Y27">
-        <v>0.99890398070122899</v>
+      <c r="W27" s="1">
+        <v>1.2663121483793499E-6</v>
+      </c>
+      <c r="X27">
+        <v>0.99884977637929395</v>
       </c>
       <c r="Z27">
         <v>8</v>
       </c>
       <c r="AA27" s="1">
-        <v>2.60451063999099E-7</v>
+        <v>2.4174717230930802E-7</v>
       </c>
       <c r="AB27">
-        <v>0.99855014266606501</v>
+        <v>0.99715380777201901</v>
       </c>
       <c r="AC27">
         <v>8</v>
       </c>
       <c r="AD27" s="1">
-        <v>2.6569800612765302E-7</v>
+        <v>2.5983967192679899E-7</v>
       </c>
       <c r="AE27">
-        <v>0.99910763909135702</v>
+        <v>0.99890398070122899</v>
       </c>
       <c r="AF27">
         <v>8</v>
       </c>
       <c r="AG27" s="1">
+        <v>2.60451063999099E-7</v>
+      </c>
+      <c r="AH27">
+        <v>0.99855014266606501</v>
+      </c>
+      <c r="AI27">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="1">
+        <v>2.6569800612765302E-7</v>
+      </c>
+      <c r="AK27">
+        <v>0.99910763909135702</v>
+      </c>
+      <c r="AL27">
+        <v>8</v>
+      </c>
+      <c r="AM27" s="1">
         <v>2.5890240838521001E-7</v>
       </c>
-      <c r="AH27">
+      <c r="AN27">
         <v>0.99634952325639903</v>
       </c>
+      <c r="AO27">
+        <v>8</v>
+      </c>
+      <c r="AP27" s="1">
+        <v>2.2112918291457299E-7</v>
+      </c>
+      <c r="AQ27">
+        <v>0.99810098338917597</v>
+      </c>
+      <c r="AR27">
+        <v>8</v>
+      </c>
+      <c r="AS27" s="1">
+        <v>2.8660552548563699E-7</v>
+      </c>
+      <c r="AT27">
+        <v>0.99909716609030796</v>
+      </c>
     </row>
-    <row r="28" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D28">
         <v>9</v>
       </c>
@@ -24820,53 +25651,89 @@
       <c r="R28">
         <v>0.99936735339787297</v>
       </c>
-      <c r="T28">
+      <c r="S28">
         <v>9</v>
       </c>
-      <c r="U28" s="1">
-        <v>2.5129490747768702E-7</v>
+      <c r="T28" s="1">
+        <v>9.0781621848739502E-7</v>
+      </c>
+      <c r="U28">
+        <v>0.99957603534596695</v>
       </c>
       <c r="V28">
-        <v>0.99695224797288196</v>
-      </c>
-      <c r="W28">
         <v>9</v>
       </c>
-      <c r="X28" s="1">
-        <v>2.5744101376284399E-7</v>
-      </c>
-      <c r="Y28">
-        <v>0.99770847711633903</v>
+      <c r="W28" s="1">
+        <v>1.5060086833133199E-6</v>
+      </c>
+      <c r="X28">
+        <v>0.99195617628593902</v>
       </c>
       <c r="Z28">
         <v>9</v>
       </c>
       <c r="AA28" s="1">
-        <v>2.5682140707267698E-7</v>
+        <v>2.5129490747768702E-7</v>
       </c>
       <c r="AB28">
-        <v>0.99810244238482504</v>
+        <v>0.99695224797288196</v>
       </c>
       <c r="AC28">
         <v>9</v>
       </c>
       <c r="AD28" s="1">
-        <v>2.4147291243531102E-7</v>
+        <v>2.5744101376284399E-7</v>
       </c>
       <c r="AE28">
-        <v>0.99692213711905897</v>
+        <v>0.99770847711633903</v>
       </c>
       <c r="AF28">
         <v>9</v>
       </c>
       <c r="AG28" s="1">
+        <v>2.5682140707267698E-7</v>
+      </c>
+      <c r="AH28">
+        <v>0.99810244238482504</v>
+      </c>
+      <c r="AI28">
+        <v>9</v>
+      </c>
+      <c r="AJ28" s="1">
+        <v>2.4147291243531102E-7</v>
+      </c>
+      <c r="AK28">
+        <v>0.99692213711905897</v>
+      </c>
+      <c r="AL28">
+        <v>9</v>
+      </c>
+      <c r="AM28" s="1">
         <v>2.3518564150603799E-7</v>
       </c>
-      <c r="AH28">
+      <c r="AN28">
         <v>0.99827408666149697</v>
       </c>
+      <c r="AO28">
+        <v>9</v>
+      </c>
+      <c r="AP28" s="1">
+        <v>2.0524999388734699E-7</v>
+      </c>
+      <c r="AQ28">
+        <v>0.99676398760928098</v>
+      </c>
+      <c r="AR28">
+        <v>9</v>
+      </c>
+      <c r="AS28" s="1">
+        <v>3.2173716264156599E-7</v>
+      </c>
+      <c r="AT28">
+        <v>0.99923712675772203</v>
+      </c>
     </row>
-    <row r="29" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D29">
         <v>10</v>
       </c>
@@ -24912,53 +25779,89 @@
       <c r="R29">
         <v>0.99921710463433</v>
       </c>
-      <c r="T29">
+      <c r="S29">
         <v>10</v>
       </c>
-      <c r="U29" s="1">
-        <v>2.6073224832370702E-7</v>
+      <c r="T29" s="1">
+        <v>9.1009672124849897E-7</v>
+      </c>
+      <c r="U29">
+        <v>0.99892559012002202</v>
       </c>
       <c r="V29">
-        <v>0.99818778475194103</v>
-      </c>
-      <c r="W29">
         <v>10</v>
       </c>
-      <c r="X29" s="1">
-        <v>2.5331696717917998E-7</v>
-      </c>
-      <c r="Y29">
-        <v>0.99825196007787498</v>
+      <c r="W29" s="1">
+        <v>1.2269353013205301E-6</v>
+      </c>
+      <c r="X29">
+        <v>0.997359747565007</v>
       </c>
       <c r="Z29">
         <v>10</v>
       </c>
       <c r="AA29" s="1">
-        <v>2.6252736703667598E-7</v>
+        <v>2.6073224832370702E-7</v>
       </c>
       <c r="AB29">
-        <v>0.99836079974740999</v>
+        <v>0.99818778475194103</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29" s="1">
-        <v>2.4818638469961799E-7</v>
+        <v>2.5331696717917998E-7</v>
       </c>
       <c r="AE29">
-        <v>0.99673960455113297</v>
+        <v>0.99825196007787498</v>
       </c>
       <c r="AF29">
         <v>10</v>
       </c>
       <c r="AG29" s="1">
+        <v>2.6252736703667598E-7</v>
+      </c>
+      <c r="AH29">
+        <v>0.99836079974740999</v>
+      </c>
+      <c r="AI29">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="1">
+        <v>2.4818638469961799E-7</v>
+      </c>
+      <c r="AK29">
+        <v>0.99673960455113297</v>
+      </c>
+      <c r="AL29">
+        <v>10</v>
+      </c>
+      <c r="AM29" s="1">
         <v>2.7055555828395698E-7</v>
       </c>
-      <c r="AH29">
+      <c r="AN29">
         <v>0.99788481561016196</v>
       </c>
+      <c r="AO29">
+        <v>10</v>
+      </c>
+      <c r="AP29" s="1">
+        <v>2.0379908132453301E-7</v>
+      </c>
+      <c r="AQ29">
+        <v>0.99547453297174704</v>
+      </c>
+      <c r="AR29">
+        <v>10</v>
+      </c>
+      <c r="AS29" s="1">
+        <v>3.2294814118353001E-7</v>
+      </c>
+      <c r="AT29">
+        <v>0.99863060090112998</v>
+      </c>
     </row>
-    <row r="30" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D30" t="s">
         <v>21</v>
       </c>
@@ -25004,53 +25907,89 @@
       <c r="R30" s="1">
         <v>5.2561995419558599E-8</v>
       </c>
-      <c r="T30" t="s">
+      <c r="S30" t="s">
         <v>21</v>
       </c>
+      <c r="T30" s="1">
+        <v>9.0358816941176504E-7</v>
+      </c>
       <c r="U30" s="1">
-        <v>2.5024402217580399E-7</v>
-      </c>
-      <c r="V30" s="1">
-        <v>1.47781235736947E-8</v>
-      </c>
-      <c r="W30" t="s">
+        <v>5.80915509189821E-8</v>
+      </c>
+      <c r="V30" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W30" s="1">
+        <v>1.3326659102040801E-6</v>
+      </c>
       <c r="X30" s="1">
-        <v>2.52651821219531E-7</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>1.78199053710023E-8</v>
+        <v>9.08043816969484E-8</v>
       </c>
       <c r="Z30" t="s">
         <v>21</v>
       </c>
       <c r="AA30" s="1">
-        <v>2.53342456378159E-7</v>
+        <v>2.5024402217580399E-7</v>
       </c>
       <c r="AB30" s="1">
-        <v>1.0668009045763501E-8</v>
+        <v>1.47781235736947E-8</v>
       </c>
       <c r="AC30" t="s">
         <v>21</v>
       </c>
       <c r="AD30" s="1">
-        <v>2.5728060049426198E-7</v>
+        <v>2.52651821219531E-7</v>
       </c>
       <c r="AE30" s="1">
-        <v>1.19453283690177E-8</v>
+        <v>1.78199053710023E-8</v>
       </c>
       <c r="AF30" t="s">
         <v>21</v>
       </c>
       <c r="AG30" s="1">
+        <v>2.53342456378159E-7</v>
+      </c>
+      <c r="AH30" s="1">
+        <v>1.0668009045763501E-8</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ30" s="1">
+        <v>2.5728060049426198E-7</v>
+      </c>
+      <c r="AK30" s="1">
+        <v>1.19453283690177E-8</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM30" s="1">
         <v>2.71646397518938E-7</v>
       </c>
-      <c r="AH30" s="1">
+      <c r="AN30" s="1">
         <v>1.85557143702556E-8</v>
       </c>
+      <c r="AO30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP30" s="1">
+        <v>2.19024020475512E-7</v>
+      </c>
+      <c r="AQ30" s="1">
+        <v>2.1244403376165702E-8</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS30" s="1">
+        <v>3.16900458245706E-7</v>
+      </c>
+      <c r="AT30" s="1">
+        <v>1.43408855213386E-8</v>
+      </c>
     </row>
-    <row r="31" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:46" x14ac:dyDescent="0.2">
       <c r="F31" s="4">
         <f>F30/E30</f>
         <v>4.5737712282544231E-2</v>
@@ -25071,28 +26010,46 @@
         <f>R30/Q30</f>
         <v>4.5341309108270569E-2</v>
       </c>
-      <c r="V31" s="4">
-        <f>V30/U30</f>
-        <v>5.9054851521338728E-2</v>
-      </c>
-      <c r="Y31" s="4">
-        <f>Y30/X30</f>
-        <v>7.0531474045930007E-2</v>
+      <c r="U31" s="4">
+        <f>U30/T30</f>
+        <v>6.4289853370700548E-2</v>
+      </c>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4">
+        <f>X30/W30</f>
+        <v>6.8137393627066598E-2</v>
       </c>
       <c r="AB31" s="4">
         <f>AB30/AA30</f>
-        <v>4.2109045590998713E-2</v>
+        <v>5.9054851521338728E-2</v>
       </c>
       <c r="AE31" s="4">
         <f>AE30/AD30</f>
-        <v>4.6429184112869448E-2</v>
+        <v>7.0531474045930007E-2</v>
       </c>
       <c r="AH31" s="4">
         <f>AH30/AG30</f>
+        <v>4.2109045590998713E-2</v>
+      </c>
+      <c r="AK31" s="4">
+        <f>AK30/AJ30</f>
+        <v>4.6429184112869448E-2</v>
+      </c>
+      <c r="AN31" s="4">
+        <f>AN30/AM30</f>
         <v>6.8308339590485379E-2</v>
       </c>
+      <c r="AQ31" s="4">
+        <f>AQ30/AP30</f>
+        <v>9.6995769368323395E-2</v>
+      </c>
+      <c r="AT31" s="4">
+        <f>AT30/AS30</f>
+        <v>4.5253596667946504E-2</v>
+      </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>22</v>
       </c>
@@ -25119,31 +26076,49 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="1"/>
-      <c r="T33" t="s">
+      <c r="S33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T33" s="2"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Z33" t="s">
         <v>5</v>
       </c>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2" t="s">
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC33" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="AD33" s="2"/>
       <c r="AE33" s="2"/>
-      <c r="AF33" s="2" t="s">
+      <c r="AF33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ33" s="2"/>
+      <c r="AK33" s="2"/>
+      <c r="AL33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG33" s="2"/>
-      <c r="AH33" s="1"/>
+      <c r="AM33" s="2"/>
+      <c r="AN33" s="1"/>
+      <c r="AO33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP33" s="2"/>
+      <c r="AQ33" s="1"/>
+      <c r="AR33" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D34">
         <v>1</v>
       </c>
@@ -25189,53 +26164,71 @@
       <c r="R34" s="1">
         <v>0.99917735444442801</v>
       </c>
-      <c r="T34">
+      <c r="S34" s="1">
         <v>1</v>
       </c>
-      <c r="U34" s="2">
-        <v>1.1886190081001999E-7</v>
-      </c>
-      <c r="V34" s="2">
-        <v>0.99659671555587503</v>
-      </c>
-      <c r="W34">
+      <c r="T34" s="1">
+        <v>6.4098716686674702E-7</v>
+      </c>
+      <c r="U34" s="1">
+        <v>0.99421897634080203</v>
+      </c>
+      <c r="V34" s="1">
         <v>1</v>
       </c>
-      <c r="X34" s="2">
-        <v>1.4911578079952E-7</v>
-      </c>
-      <c r="Y34" s="2">
-        <v>0.99617433595240001</v>
+      <c r="W34" s="1">
+        <v>1.0078179851140501E-6</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0.99943055239460299</v>
       </c>
       <c r="Z34">
         <v>1</v>
       </c>
-      <c r="AA34" s="1">
-        <v>1.2740577338183501E-7</v>
-      </c>
-      <c r="AB34">
-        <v>0.97901749990998999</v>
+      <c r="AA34" s="2">
+        <v>1.1886190081001999E-7</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>0.99659671555587503</v>
       </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AD34" s="2">
+        <v>1.4911578079952E-7</v>
+      </c>
+      <c r="AE34" s="2">
+        <v>0.99617433595240001</v>
+      </c>
+      <c r="AF34">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="1">
+        <v>1.2740577338183501E-7</v>
+      </c>
+      <c r="AH34">
+        <v>0.97901749990998999</v>
+      </c>
+      <c r="AI34">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="2">
         <v>1.5206036047401201E-7</v>
       </c>
-      <c r="AE34" s="2">
+      <c r="AK34" s="2">
         <v>0.99869540883437102</v>
       </c>
-      <c r="AF34" s="2">
+      <c r="AL34" s="2">
         <v>1</v>
       </c>
-      <c r="AG34" s="2">
+      <c r="AM34" s="2">
         <v>1.6673833924098101E-7</v>
       </c>
-      <c r="AH34" s="1">
+      <c r="AN34" s="1">
         <v>0.99620782809779995</v>
       </c>
     </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D35">
         <v>2</v>
       </c>
@@ -25281,53 +26274,71 @@
       <c r="R35" s="1">
         <v>0.99860600164857005</v>
       </c>
-      <c r="T35">
+      <c r="S35" s="1">
         <v>2</v>
       </c>
+      <c r="T35" s="1">
+        <v>6.33432872989195E-7</v>
+      </c>
       <c r="U35" s="1">
-        <v>1.53102722905573E-7</v>
-      </c>
-      <c r="V35">
-        <v>0.997500200288856</v>
-      </c>
-      <c r="W35">
+        <v>0.99874634228374404</v>
+      </c>
+      <c r="V35" s="1">
         <v>2</v>
       </c>
+      <c r="W35" s="1">
+        <v>9.9554269483793593E-7</v>
+      </c>
       <c r="X35" s="1">
-        <v>1.33221236668417E-7</v>
-      </c>
-      <c r="Y35">
-        <v>0.99773972215117201</v>
+        <v>0.99740301192926895</v>
       </c>
       <c r="Z35">
         <v>2</v>
       </c>
       <c r="AA35" s="1">
-        <v>1.2648213783094599E-7</v>
+        <v>1.53102722905573E-7</v>
       </c>
       <c r="AB35">
-        <v>0.99038604545575204</v>
+        <v>0.997500200288856</v>
       </c>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AD35" s="1">
-        <v>1.44883801125028E-7</v>
+        <v>1.33221236668417E-7</v>
       </c>
       <c r="AE35">
-        <v>0.998072839124588</v>
+        <v>0.99773972215117201</v>
       </c>
       <c r="AF35">
         <v>2</v>
       </c>
       <c r="AG35" s="1">
+        <v>1.2648213783094599E-7</v>
+      </c>
+      <c r="AH35">
+        <v>0.99038604545575204</v>
+      </c>
+      <c r="AI35">
+        <v>2</v>
+      </c>
+      <c r="AJ35" s="1">
+        <v>1.44883801125028E-7</v>
+      </c>
+      <c r="AK35">
+        <v>0.998072839124588</v>
+      </c>
+      <c r="AL35">
+        <v>2</v>
+      </c>
+      <c r="AM35" s="1">
         <v>1.43363994929873E-7</v>
       </c>
-      <c r="AH35">
+      <c r="AN35">
         <v>0.99385025199993005</v>
       </c>
     </row>
-    <row r="36" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D36">
         <v>3</v>
       </c>
@@ -25373,53 +26384,71 @@
       <c r="R36" s="1">
         <v>0.99861650657155199</v>
       </c>
-      <c r="T36">
+      <c r="S36" s="1">
         <v>3</v>
       </c>
+      <c r="T36" s="1">
+        <v>7.08834917166867E-7</v>
+      </c>
       <c r="U36" s="1">
-        <v>1.47099971304283E-7</v>
-      </c>
-      <c r="V36">
-        <v>0.99748914174444203</v>
-      </c>
-      <c r="W36">
+        <v>0.99597332623613999</v>
+      </c>
+      <c r="V36" s="1">
         <v>3</v>
       </c>
+      <c r="W36" s="1">
+        <v>1.0387429066026399E-6</v>
+      </c>
       <c r="X36" s="1">
-        <v>1.4126295773644299E-7</v>
-      </c>
-      <c r="Y36">
-        <v>0.990026128458524</v>
+        <v>0.99904928480902799</v>
       </c>
       <c r="Z36">
         <v>3</v>
       </c>
       <c r="AA36" s="1">
-        <v>1.57827053318833E-7</v>
+        <v>1.47099971304283E-7</v>
       </c>
       <c r="AB36">
-        <v>0.99468480926573699</v>
+        <v>0.99748914174444203</v>
       </c>
       <c r="AC36">
         <v>3</v>
       </c>
       <c r="AD36" s="1">
-        <v>1.3864125640891001E-7</v>
+        <v>1.4126295773644299E-7</v>
       </c>
       <c r="AE36">
-        <v>0.99838363067806002</v>
+        <v>0.990026128458524</v>
       </c>
       <c r="AF36">
         <v>3</v>
       </c>
       <c r="AG36" s="1">
+        <v>1.57827053318833E-7</v>
+      </c>
+      <c r="AH36">
+        <v>0.99468480926573699</v>
+      </c>
+      <c r="AI36">
+        <v>3</v>
+      </c>
+      <c r="AJ36" s="1">
+        <v>1.3864125640891001E-7</v>
+      </c>
+      <c r="AK36">
+        <v>0.99838363067806002</v>
+      </c>
+      <c r="AL36">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="1">
         <v>1.51681779239481E-7</v>
       </c>
-      <c r="AH36">
+      <c r="AN36">
         <v>0.99616455439356699</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D37">
         <v>4</v>
       </c>
@@ -25465,53 +26494,71 @@
       <c r="R37" s="1">
         <v>0.99829736765270505</v>
       </c>
-      <c r="T37">
+      <c r="S37" s="1">
         <v>4</v>
       </c>
+      <c r="T37" s="1">
+        <v>4.9889559567827096E-7</v>
+      </c>
       <c r="U37" s="1">
-        <v>1.2914034087602201E-7</v>
-      </c>
-      <c r="V37">
-        <v>0.99295450377592198</v>
-      </c>
-      <c r="W37">
+        <v>0.99589881203442698</v>
+      </c>
+      <c r="V37" s="1">
         <v>4</v>
       </c>
+      <c r="W37" s="1">
+        <v>9.8988184681872791E-7</v>
+      </c>
       <c r="X37" s="1">
-        <v>1.38250845323633E-7</v>
-      </c>
-      <c r="Y37">
-        <v>0.99692351993695105</v>
+        <v>0.99916265368498902</v>
       </c>
       <c r="Z37">
         <v>4</v>
       </c>
       <c r="AA37" s="1">
-        <v>1.36329193639841E-7</v>
+        <v>1.2914034087602201E-7</v>
       </c>
       <c r="AB37">
-        <v>0.99656671370842898</v>
+        <v>0.99295450377592198</v>
       </c>
       <c r="AC37">
         <v>4</v>
       </c>
       <c r="AD37" s="1">
-        <v>1.5512481559289E-7</v>
+        <v>1.38250845323633E-7</v>
       </c>
       <c r="AE37">
-        <v>0.99617262072769297</v>
+        <v>0.99692351993695105</v>
       </c>
       <c r="AF37">
         <v>4</v>
       </c>
       <c r="AG37" s="1">
+        <v>1.36329193639841E-7</v>
+      </c>
+      <c r="AH37">
+        <v>0.99656671370842898</v>
+      </c>
+      <c r="AI37">
+        <v>4</v>
+      </c>
+      <c r="AJ37" s="1">
+        <v>1.5512481559289E-7</v>
+      </c>
+      <c r="AK37">
+        <v>0.99617262072769297</v>
+      </c>
+      <c r="AL37">
+        <v>4</v>
+      </c>
+      <c r="AM37" s="1">
         <v>1.39102581677042E-7</v>
       </c>
-      <c r="AH37">
+      <c r="AN37">
         <v>0.993786614665785</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D38">
         <v>5</v>
       </c>
@@ -25557,53 +26604,71 @@
       <c r="R38" s="1">
         <v>0.99878125164046505</v>
       </c>
-      <c r="T38">
+      <c r="S38" s="1">
         <v>5</v>
       </c>
+      <c r="T38" s="1">
+        <v>7.0476904249699896E-7</v>
+      </c>
       <c r="U38" s="1">
-        <v>1.65257856881422E-7</v>
-      </c>
-      <c r="V38">
-        <v>0.99702822164917204</v>
-      </c>
-      <c r="W38">
+        <v>0.99865414562324295</v>
+      </c>
+      <c r="V38" s="1">
         <v>5</v>
       </c>
+      <c r="W38" s="1">
+        <v>1.0230387515005999E-6</v>
+      </c>
       <c r="X38" s="1">
-        <v>1.5567913489837199E-7</v>
-      </c>
-      <c r="Y38">
-        <v>0.99671500307257599</v>
+        <v>0.999522716660877</v>
       </c>
       <c r="Z38">
         <v>5</v>
       </c>
       <c r="AA38" s="1">
-        <v>1.5458916296407399E-7</v>
+        <v>1.65257856881422E-7</v>
       </c>
       <c r="AB38">
-        <v>0.99740286621103302</v>
+        <v>0.99702822164917204</v>
       </c>
       <c r="AC38">
         <v>5</v>
       </c>
       <c r="AD38" s="1">
-        <v>1.67235397577439E-7</v>
+        <v>1.5567913489837199E-7</v>
       </c>
       <c r="AE38">
-        <v>0.99775973278163499</v>
+        <v>0.99671500307257599</v>
       </c>
       <c r="AF38">
         <v>5</v>
       </c>
       <c r="AG38" s="1">
+        <v>1.5458916296407399E-7</v>
+      </c>
+      <c r="AH38">
+        <v>0.99740286621103302</v>
+      </c>
+      <c r="AI38">
+        <v>5</v>
+      </c>
+      <c r="AJ38" s="1">
+        <v>1.67235397577439E-7</v>
+      </c>
+      <c r="AK38">
+        <v>0.99775973278163499</v>
+      </c>
+      <c r="AL38">
+        <v>5</v>
+      </c>
+      <c r="AM38" s="1">
         <v>1.1839916195154901E-7</v>
       </c>
-      <c r="AH38">
+      <c r="AN38">
         <v>0.97135960271119903</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D39">
         <v>6</v>
       </c>
@@ -25649,53 +26714,71 @@
       <c r="R39" s="1">
         <v>0.99660978189293004</v>
       </c>
-      <c r="T39">
+      <c r="S39" s="1">
         <v>6</v>
       </c>
+      <c r="T39" s="1">
+        <v>6.3211516878751397E-7</v>
+      </c>
       <c r="U39" s="1">
-        <v>1.4211178861471499E-7</v>
-      </c>
-      <c r="V39">
-        <v>0.99335207309319296</v>
-      </c>
-      <c r="W39">
+        <v>0.99803589122104797</v>
+      </c>
+      <c r="V39" s="1">
         <v>6</v>
       </c>
+      <c r="W39" s="1">
+        <v>1.2200295711884801E-6</v>
+      </c>
       <c r="X39" s="1">
-        <v>1.4144330219005499E-7</v>
-      </c>
-      <c r="Y39">
-        <v>0.998019177924232</v>
+        <v>0.98819005107174696</v>
       </c>
       <c r="Z39">
         <v>6</v>
       </c>
       <c r="AA39" s="1">
-        <v>1.2667417005925101E-7</v>
+        <v>1.4211178861471499E-7</v>
       </c>
       <c r="AB39">
-        <v>0.98576704068072296</v>
+        <v>0.99335207309319296</v>
       </c>
       <c r="AC39">
         <v>6</v>
       </c>
       <c r="AD39" s="1">
-        <v>1.53277976816921E-7</v>
+        <v>1.4144330219005499E-7</v>
       </c>
       <c r="AE39">
-        <v>0.99751802086420405</v>
+        <v>0.998019177924232</v>
       </c>
       <c r="AF39">
         <v>6</v>
       </c>
       <c r="AG39" s="1">
+        <v>1.2667417005925101E-7</v>
+      </c>
+      <c r="AH39">
+        <v>0.98576704068072296</v>
+      </c>
+      <c r="AI39">
+        <v>6</v>
+      </c>
+      <c r="AJ39" s="1">
+        <v>1.53277976816921E-7</v>
+      </c>
+      <c r="AK39">
+        <v>0.99751802086420405</v>
+      </c>
+      <c r="AL39">
+        <v>6</v>
+      </c>
+      <c r="AM39" s="1">
         <v>1.5923651249531201E-7</v>
       </c>
-      <c r="AH39">
+      <c r="AN39">
         <v>0.99599910150331805</v>
       </c>
     </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D40">
         <v>7</v>
       </c>
@@ -25741,53 +26824,71 @@
       <c r="R40" s="3">
         <v>0.99912511319573505</v>
       </c>
-      <c r="T40">
+      <c r="S40" s="3">
         <v>7</v>
       </c>
-      <c r="U40" s="1">
-        <v>1.34956266504163E-7</v>
-      </c>
-      <c r="V40">
-        <v>0.994918633034648</v>
-      </c>
-      <c r="W40">
+      <c r="T40" s="3">
+        <v>7.2163247442977198E-7</v>
+      </c>
+      <c r="U40" s="3">
+        <v>0.99235247358376399</v>
+      </c>
+      <c r="V40" s="3">
         <v>7</v>
       </c>
-      <c r="X40" s="1">
-        <v>1.4669480438760999E-7</v>
-      </c>
-      <c r="Y40">
-        <v>0.99728328992023396</v>
+      <c r="W40" s="3">
+        <v>9.9060341896758797E-7</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0.99856988443961603</v>
       </c>
       <c r="Z40">
         <v>7</v>
       </c>
       <c r="AA40" s="1">
-        <v>1.3281364126603101E-7</v>
+        <v>1.34956266504163E-7</v>
       </c>
       <c r="AB40">
-        <v>0.99417832000888295</v>
+        <v>0.994918633034648</v>
       </c>
       <c r="AC40">
         <v>7</v>
       </c>
       <c r="AD40" s="1">
-        <v>1.6550633276831901E-7</v>
+        <v>1.4669480438760999E-7</v>
       </c>
       <c r="AE40">
-        <v>0.99888514321856003</v>
+        <v>0.99728328992023396</v>
       </c>
       <c r="AF40">
         <v>7</v>
       </c>
       <c r="AG40" s="1">
+        <v>1.3281364126603101E-7</v>
+      </c>
+      <c r="AH40">
+        <v>0.99417832000888295</v>
+      </c>
+      <c r="AI40">
+        <v>7</v>
+      </c>
+      <c r="AJ40" s="1">
+        <v>1.6550633276831901E-7</v>
+      </c>
+      <c r="AK40">
+        <v>0.99888514321856003</v>
+      </c>
+      <c r="AL40">
+        <v>7</v>
+      </c>
+      <c r="AM40" s="1">
         <v>1.59459521795545E-7</v>
       </c>
-      <c r="AH40">
+      <c r="AN40">
         <v>0.99821212850654595</v>
       </c>
     </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D41">
         <v>8</v>
       </c>
@@ -25833,53 +26934,71 @@
       <c r="R41">
         <v>0.99830187653681501</v>
       </c>
-      <c r="T41">
+      <c r="S41">
         <v>8</v>
       </c>
-      <c r="U41" s="1">
-        <v>1.4198349008475201E-7</v>
+      <c r="T41" s="1">
+        <v>7.3188525570228096E-7</v>
+      </c>
+      <c r="U41">
+        <v>0.99430559443416899</v>
       </c>
       <c r="V41">
-        <v>0.99627486717562297</v>
-      </c>
-      <c r="W41">
         <v>8</v>
       </c>
-      <c r="X41" s="1">
-        <v>1.5323144758118899E-7</v>
-      </c>
-      <c r="Y41">
-        <v>0.99590265791478105</v>
+      <c r="W41" s="1">
+        <v>1.0314189877550999E-6</v>
+      </c>
+      <c r="X41">
+        <v>0.99884904269054298</v>
       </c>
       <c r="Z41">
         <v>8</v>
       </c>
       <c r="AA41" s="1">
-        <v>1.3900852890572299E-7</v>
+        <v>1.4198349008475201E-7</v>
       </c>
       <c r="AB41">
-        <v>0.99423602801861899</v>
+        <v>0.99627486717562297</v>
       </c>
       <c r="AC41">
         <v>8</v>
       </c>
       <c r="AD41" s="1">
-        <v>1.5812441167779201E-7</v>
+        <v>1.5323144758118899E-7</v>
       </c>
       <c r="AE41">
-        <v>0.99567038941498498</v>
+        <v>0.99590265791478105</v>
       </c>
       <c r="AF41">
         <v>8</v>
       </c>
       <c r="AG41" s="1">
+        <v>1.3900852890572299E-7</v>
+      </c>
+      <c r="AH41">
+        <v>0.99423602801861899</v>
+      </c>
+      <c r="AI41">
+        <v>8</v>
+      </c>
+      <c r="AJ41" s="1">
+        <v>1.5812441167779201E-7</v>
+      </c>
+      <c r="AK41">
+        <v>0.99567038941498498</v>
+      </c>
+      <c r="AL41">
+        <v>8</v>
+      </c>
+      <c r="AM41" s="1">
         <v>1.4713622889822299E-7</v>
       </c>
-      <c r="AH41">
+      <c r="AN41">
         <v>0.996448952471509</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D42">
         <v>9</v>
       </c>
@@ -25925,53 +27044,71 @@
       <c r="R42">
         <v>0.99722505689936303</v>
       </c>
-      <c r="T42">
+      <c r="S42">
         <v>9</v>
       </c>
-      <c r="U42" s="1">
-        <v>1.44611476246906E-7</v>
+      <c r="T42" s="1">
+        <v>7.2837501032413004E-7</v>
+      </c>
+      <c r="U42">
+        <v>0.99767933552641497</v>
       </c>
       <c r="V42">
-        <v>0.99465179793223402</v>
-      </c>
-      <c r="W42">
         <v>9</v>
       </c>
-      <c r="X42" s="1">
-        <v>1.2590170415510401E-7</v>
-      </c>
-      <c r="Y42">
-        <v>0.993358880564992</v>
+      <c r="W42" s="1">
+        <v>1.0426278655462199E-6</v>
+      </c>
+      <c r="X42">
+        <v>0.99919215302228304</v>
       </c>
       <c r="Z42">
         <v>9</v>
       </c>
       <c r="AA42" s="1">
-        <v>1.2132274709367699E-7</v>
+        <v>1.44611476246906E-7</v>
       </c>
       <c r="AB42">
-        <v>0.99546512248559604</v>
+        <v>0.99465179793223402</v>
       </c>
       <c r="AC42">
         <v>9</v>
       </c>
       <c r="AD42" s="1">
-        <v>1.44051710335258E-7</v>
+        <v>1.2590170415510401E-7</v>
       </c>
       <c r="AE42">
-        <v>0.99621100688878905</v>
+        <v>0.993358880564992</v>
       </c>
       <c r="AF42">
         <v>9</v>
       </c>
       <c r="AG42" s="1">
+        <v>1.2132274709367699E-7</v>
+      </c>
+      <c r="AH42">
+        <v>0.99546512248559604</v>
+      </c>
+      <c r="AI42">
+        <v>9</v>
+      </c>
+      <c r="AJ42" s="1">
+        <v>1.44051710335258E-7</v>
+      </c>
+      <c r="AK42">
+        <v>0.99621100688878905</v>
+      </c>
+      <c r="AL42">
+        <v>9</v>
+      </c>
+      <c r="AM42" s="1">
         <v>1.57796684744619E-7</v>
       </c>
-      <c r="AH42">
+      <c r="AN42">
         <v>0.99448089543229101</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D43">
         <v>10</v>
       </c>
@@ -26017,53 +27154,71 @@
       <c r="R43">
         <v>0.99922697755016099</v>
       </c>
-      <c r="T43">
+      <c r="S43">
         <v>10</v>
       </c>
-      <c r="U43" s="1">
-        <v>1.5684480443261001E-7</v>
+      <c r="T43" s="1">
+        <v>5.3144953085234099E-7</v>
+      </c>
+      <c r="U43">
+        <v>0.997808815517081</v>
       </c>
       <c r="V43">
-        <v>0.99912592719284998</v>
-      </c>
-      <c r="W43">
         <v>10</v>
       </c>
-      <c r="X43" s="1">
-        <v>1.5363169892747299E-7</v>
-      </c>
-      <c r="Y43">
-        <v>0.99650257924359598</v>
+      <c r="W43" s="1">
+        <v>1.09270649795918E-6</v>
+      </c>
+      <c r="X43">
+        <v>0.99933999886386604</v>
       </c>
       <c r="Z43">
         <v>10</v>
       </c>
       <c r="AA43" s="1">
-        <v>1.5426270701267501E-7</v>
+        <v>1.5684480443261001E-7</v>
       </c>
       <c r="AB43">
-        <v>0.987705839976601</v>
+        <v>0.99912592719284998</v>
       </c>
       <c r="AC43">
         <v>10</v>
       </c>
       <c r="AD43" s="1">
-        <v>1.69996163436586E-7</v>
+        <v>1.5363169892747299E-7</v>
       </c>
       <c r="AE43">
-        <v>0.99520315774865098</v>
+        <v>0.99650257924359598</v>
       </c>
       <c r="AF43">
         <v>10</v>
       </c>
       <c r="AG43" s="1">
+        <v>1.5426270701267501E-7</v>
+      </c>
+      <c r="AH43">
+        <v>0.987705839976601</v>
+      </c>
+      <c r="AI43">
+        <v>10</v>
+      </c>
+      <c r="AJ43" s="1">
+        <v>1.69996163436586E-7</v>
+      </c>
+      <c r="AK43">
+        <v>0.99520315774865098</v>
+      </c>
+      <c r="AL43">
+        <v>10</v>
+      </c>
+      <c r="AM43" s="1">
         <v>1.5467634748368701E-7</v>
       </c>
-      <c r="AH43">
+      <c r="AN43">
         <v>0.99760918545670796</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D44" t="s">
         <v>21</v>
       </c>
@@ -26109,53 +27264,71 @@
       <c r="R44" s="1">
         <v>3.7085037986431402E-8</v>
       </c>
-      <c r="T44" t="s">
+      <c r="S44" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="T44" s="1">
+        <v>6.5323770352941203E-7</v>
+      </c>
       <c r="U44" s="1">
-        <v>1.4339706186604699E-7</v>
-      </c>
-      <c r="V44" s="1">
-        <v>1.35328723071575E-8</v>
-      </c>
-      <c r="W44" t="s">
+        <v>8.2930854583018405E-8</v>
+      </c>
+      <c r="V44" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W44" s="1">
+        <v>1.0432410526290499E-6</v>
+      </c>
       <c r="X44" s="1">
-        <v>1.43843291266782E-7</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>9.6516549141585397E-9</v>
+        <v>6.9456114402721206E-8</v>
       </c>
       <c r="Z44" t="s">
         <v>21</v>
       </c>
       <c r="AA44" s="1">
-        <v>1.3767151154728899E-7</v>
+        <v>1.4339706186604699E-7</v>
       </c>
       <c r="AB44" s="1">
-        <v>1.3390377889430399E-8</v>
+        <v>1.35328723071575E-8</v>
       </c>
       <c r="AC44" t="s">
         <v>21</v>
       </c>
       <c r="AD44" s="1">
-        <v>1.54890222621316E-7</v>
+        <v>1.43843291266782E-7</v>
       </c>
       <c r="AE44" s="1">
-        <v>1.0520074878246401E-8</v>
+        <v>9.6516549141585397E-9</v>
       </c>
       <c r="AF44" t="s">
         <v>21</v>
       </c>
       <c r="AG44" s="1">
+        <v>1.3767151154728899E-7</v>
+      </c>
+      <c r="AH44" s="1">
+        <v>1.3390377889430399E-8</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ44" s="1">
+        <v>1.54890222621316E-7</v>
+      </c>
+      <c r="AK44" s="1">
+        <v>1.0520074878246401E-8</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM44" s="1">
         <v>1.4975911524563101E-7</v>
       </c>
-      <c r="AH44" s="1">
+      <c r="AN44" s="1">
         <v>1.37819398790323E-8</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="F45" s="4">
         <f>F44/E44</f>
         <v>5.3975921816629191E-2</v>
@@ -26176,28 +27349,40 @@
         <f>R44/Q44</f>
         <v>4.1150938000940052E-2</v>
       </c>
-      <c r="V45" s="4">
-        <f>V44/U44</f>
-        <v>9.4373428095752096E-2</v>
-      </c>
-      <c r="Y45" s="4">
-        <f>Y44/X44</f>
-        <v>6.7098401525434323E-2</v>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4">
+        <f>U44/T44</f>
+        <v>0.12695356397058372</v>
+      </c>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4">
+        <f>X44/W44</f>
+        <v>6.6577244278957684E-2</v>
       </c>
       <c r="AB45" s="4">
         <f>AB44/AA44</f>
-        <v>9.72632445081488E-2</v>
+        <v>9.4373428095752096E-2</v>
       </c>
       <c r="AE45" s="4">
         <f>AE44/AD44</f>
-        <v>6.7919554250796377E-2</v>
+        <v>6.7098401525434323E-2</v>
       </c>
       <c r="AH45" s="4">
         <f>AH44/AG44</f>
+        <v>9.72632445081488E-2</v>
+      </c>
+      <c r="AK45" s="4">
+        <f>AK44/AJ44</f>
+        <v>6.7919554250796377E-2</v>
+      </c>
+      <c r="AN45" s="4">
+        <f>AN44/AM44</f>
         <v>9.2027385821741262E-2</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>25</v>
       </c>
@@ -26224,31 +27409,49 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" s="1"/>
-      <c r="T47" t="s">
+      <c r="S47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T47" s="2"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Z47" t="s">
         <v>5</v>
       </c>
-      <c r="U47" s="2"/>
-      <c r="V47" s="2"/>
-      <c r="W47" s="2" t="s">
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC47" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="AD47" s="2"/>
       <c r="AE47" s="2"/>
-      <c r="AF47" s="2" t="s">
+      <c r="AF47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ47" s="2"/>
+      <c r="AK47" s="2"/>
+      <c r="AL47" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG47" s="2"/>
-      <c r="AH47" s="1"/>
+      <c r="AM47" s="2"/>
+      <c r="AN47" s="1"/>
+      <c r="AO47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP47" s="2"/>
+      <c r="AQ47" s="1"/>
+      <c r="AR47" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="D48">
         <v>1</v>
       </c>
@@ -26294,53 +27497,71 @@
       <c r="R48" s="1">
         <v>0.99836760036822803</v>
       </c>
-      <c r="T48">
+      <c r="S48" s="1">
         <v>1</v>
       </c>
-      <c r="U48" s="2">
+      <c r="T48" s="1">
+        <v>3.9847947851140399E-7</v>
+      </c>
+      <c r="U48" s="1">
+        <v>0.99839869439143802</v>
+      </c>
+      <c r="V48" s="1">
+        <v>1</v>
+      </c>
+      <c r="W48" s="1">
+        <v>7.6630926482593104E-7</v>
+      </c>
+      <c r="X48" s="1">
+        <v>0.99855374905528205</v>
+      </c>
+      <c r="Z48">
+        <v>1</v>
+      </c>
+      <c r="AA48" s="2">
         <v>4.52971344558615E-8</v>
       </c>
-      <c r="V48" s="2">
+      <c r="AB48" s="2">
         <v>0.89472563575202901</v>
-      </c>
-      <c r="W48" s="2">
-        <v>1</v>
-      </c>
-      <c r="X48" s="2">
-        <v>6.3744995792394598E-8</v>
-      </c>
-      <c r="Y48" s="2">
-        <v>0.99205714133635603</v>
-      </c>
-      <c r="Z48" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA48" s="1">
-        <v>6.6432855643890994E-8</v>
-      </c>
-      <c r="AB48">
-        <v>0.98770647616354101</v>
       </c>
       <c r="AC48" s="2">
         <v>1</v>
       </c>
       <c r="AD48" s="2">
+        <v>6.3744995792394598E-8</v>
+      </c>
+      <c r="AE48" s="2">
+        <v>0.99205714133635603</v>
+      </c>
+      <c r="AF48" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="1">
+        <v>6.6432855643890994E-8</v>
+      </c>
+      <c r="AH48">
+        <v>0.98770647616354101</v>
+      </c>
+      <c r="AI48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ48" s="2">
         <v>7.9638416035400804E-8</v>
       </c>
-      <c r="AE48" s="2">
+      <c r="AK48" s="2">
         <v>0.99548963748571695</v>
       </c>
-      <c r="AF48" s="2">
+      <c r="AL48" s="2">
         <v>1</v>
       </c>
-      <c r="AG48" s="2">
+      <c r="AM48" s="2">
         <v>6.6182855748893799E-8</v>
       </c>
-      <c r="AH48" s="1">
+      <c r="AN48" s="1">
         <v>0.99752695414405002</v>
       </c>
     </row>
-    <row r="49" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D49">
         <v>2</v>
       </c>
@@ -26386,53 +27607,71 @@
       <c r="R49" s="1">
         <v>0.99763318156353298</v>
       </c>
-      <c r="T49">
+      <c r="S49" s="1">
         <v>2</v>
       </c>
+      <c r="T49" s="1">
+        <v>4.24703721488595E-7</v>
+      </c>
       <c r="U49" s="1">
-        <v>6.9393801995049902E-8</v>
-      </c>
-      <c r="V49">
-        <v>0.99453848647445497</v>
-      </c>
-      <c r="W49">
+        <v>0.99397826042874904</v>
+      </c>
+      <c r="V49" s="1">
         <v>2</v>
       </c>
+      <c r="W49" s="1">
+        <v>7.4469384585834301E-7</v>
+      </c>
       <c r="X49" s="1">
-        <v>5.7177668686717097E-8</v>
-      </c>
-      <c r="Y49">
-        <v>0.96279646837419697</v>
+        <v>0.99890858063319898</v>
       </c>
       <c r="Z49">
         <v>2</v>
       </c>
       <c r="AA49" s="1">
-        <v>8.2713493729843301E-8</v>
+        <v>6.9393801995049902E-8</v>
       </c>
       <c r="AB49">
-        <v>0.99301257750924099</v>
+        <v>0.99453848647445497</v>
       </c>
       <c r="AC49">
         <v>2</v>
       </c>
       <c r="AD49" s="1">
-        <v>5.0760359566489102E-8</v>
+        <v>5.7177668686717097E-8</v>
       </c>
       <c r="AE49">
-        <v>0.97897521533119003</v>
+        <v>0.96279646837419697</v>
       </c>
       <c r="AF49">
         <v>2</v>
       </c>
       <c r="AG49" s="1">
+        <v>8.2713493729843301E-8</v>
+      </c>
+      <c r="AH49">
+        <v>0.99301257750924099</v>
+      </c>
+      <c r="AI49">
+        <v>2</v>
+      </c>
+      <c r="AJ49" s="1">
+        <v>5.0760359566489102E-8</v>
+      </c>
+      <c r="AK49">
+        <v>0.97897521533119003</v>
+      </c>
+      <c r="AL49">
+        <v>2</v>
+      </c>
+      <c r="AM49" s="1">
         <v>5.5702537223430603E-8</v>
       </c>
-      <c r="AH49">
+      <c r="AN49">
         <v>0.96291210680904504</v>
       </c>
     </row>
-    <row r="50" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D50">
         <v>3</v>
       </c>
@@ -26478,53 +27717,71 @@
       <c r="R50" s="1">
         <v>0.99754429381633303</v>
       </c>
-      <c r="T50">
+      <c r="S50" s="1">
         <v>3</v>
       </c>
+      <c r="T50" s="1">
+        <v>4.6741827515006001E-7</v>
+      </c>
       <c r="U50" s="1">
-        <v>5.94120448586215E-8</v>
-      </c>
-      <c r="V50">
-        <v>0.98546459582031498</v>
-      </c>
-      <c r="W50">
+        <v>0.99797306603250902</v>
+      </c>
+      <c r="V50" s="1">
         <v>3</v>
       </c>
+      <c r="W50" s="1">
+        <v>7.6871787082833096E-7</v>
+      </c>
       <c r="X50" s="1">
-        <v>5.2113828665716701E-8</v>
-      </c>
-      <c r="Y50">
-        <v>0.97801542231854699</v>
+        <v>0.99789107256679999</v>
       </c>
       <c r="Z50">
         <v>3</v>
       </c>
       <c r="AA50" s="1">
-        <v>6.8965892079801994E-8</v>
+        <v>5.94120448586215E-8</v>
       </c>
       <c r="AB50">
-        <v>0.99227347936050803</v>
+        <v>0.98546459582031498</v>
       </c>
       <c r="AC50">
         <v>3</v>
       </c>
       <c r="AD50" s="1">
-        <v>4.9317032625815597E-8</v>
+        <v>5.2113828665716701E-8</v>
       </c>
       <c r="AE50">
-        <v>0.96201155552528705</v>
+        <v>0.97801542231854699</v>
       </c>
       <c r="AF50">
         <v>3</v>
       </c>
       <c r="AG50" s="1">
+        <v>6.8965892079801994E-8</v>
+      </c>
+      <c r="AH50">
+        <v>0.99227347936050803</v>
+      </c>
+      <c r="AI50">
+        <v>3</v>
+      </c>
+      <c r="AJ50" s="1">
+        <v>4.9317032625815597E-8</v>
+      </c>
+      <c r="AK50">
+        <v>0.96201155552528705</v>
+      </c>
+      <c r="AL50">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="1">
         <v>8.0931747566189203E-8</v>
       </c>
-      <c r="AH50">
+      <c r="AN50">
         <v>0.99465031714482399</v>
       </c>
     </row>
-    <row r="51" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D51">
         <v>4</v>
       </c>
@@ -26570,53 +27827,71 @@
       <c r="R51" s="1">
         <v>0.99848034932239904</v>
       </c>
-      <c r="T51">
+      <c r="S51" s="1">
         <v>4</v>
       </c>
+      <c r="T51" s="1">
+        <v>4.64570508523409E-7</v>
+      </c>
       <c r="U51" s="1">
-        <v>7.2277105227630698E-8</v>
-      </c>
-      <c r="V51">
-        <v>0.99224078192349796</v>
-      </c>
-      <c r="W51">
+        <v>0.997341351498643</v>
+      </c>
+      <c r="V51" s="1">
         <v>4</v>
       </c>
+      <c r="W51" s="1">
+        <v>7.7050586170468096E-7</v>
+      </c>
       <c r="X51" s="1">
-        <v>6.3040390737268501E-8</v>
-      </c>
-      <c r="Y51">
-        <v>0.98912027818559201</v>
+        <v>0.99924553312669995</v>
       </c>
       <c r="Z51">
         <v>4</v>
       </c>
       <c r="AA51" s="1">
-        <v>6.2206025088127206E-8</v>
+        <v>7.2277105227630698E-8</v>
       </c>
       <c r="AB51">
-        <v>0.99211548069806699</v>
+        <v>0.99224078192349796</v>
       </c>
       <c r="AC51">
         <v>4</v>
       </c>
       <c r="AD51" s="1">
-        <v>7.50249631890798E-8</v>
+        <v>6.3040390737268501E-8</v>
       </c>
       <c r="AE51">
-        <v>0.98927287310794199</v>
+        <v>0.98912027818559201</v>
       </c>
       <c r="AF51">
         <v>4</v>
       </c>
       <c r="AG51" s="1">
+        <v>6.2206025088127206E-8</v>
+      </c>
+      <c r="AH51">
+        <v>0.99211548069806699</v>
+      </c>
+      <c r="AI51">
+        <v>4</v>
+      </c>
+      <c r="AJ51" s="1">
+        <v>7.50249631890798E-8</v>
+      </c>
+      <c r="AK51">
+        <v>0.98927287310794199</v>
+      </c>
+      <c r="AL51">
+        <v>4</v>
+      </c>
+      <c r="AM51" s="1">
         <v>8.1616348518712997E-8</v>
       </c>
-      <c r="AH51">
+      <c r="AN51">
         <v>0.99512875611955798</v>
       </c>
     </row>
-    <row r="52" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D52">
         <v>5</v>
       </c>
@@ -26662,53 +27937,71 @@
       <c r="R52" s="1">
         <v>0.99502871104587198</v>
       </c>
-      <c r="T52">
+      <c r="S52" s="1">
         <v>5</v>
       </c>
+      <c r="T52" s="1">
+        <v>5.28288515246099E-7</v>
+      </c>
       <c r="U52" s="1">
-        <v>8.2312858216455397E-8</v>
-      </c>
-      <c r="V52">
-        <v>0.99394608676289198</v>
-      </c>
-      <c r="W52">
+        <v>0.99505926893570895</v>
+      </c>
+      <c r="V52" s="1">
         <v>5</v>
       </c>
+      <c r="W52" s="1">
+        <v>7.9455228907563001E-7</v>
+      </c>
       <c r="X52" s="1">
-        <v>9.10293898931728E-8</v>
-      </c>
-      <c r="Y52">
-        <v>0.99535431121926898</v>
+        <v>0.99811250727930201</v>
       </c>
       <c r="Z52">
         <v>5</v>
       </c>
       <c r="AA52" s="1">
-        <v>7.6274037538438503E-8</v>
+        <v>8.2312858216455397E-8</v>
       </c>
       <c r="AB52">
-        <v>0.95961848311116504</v>
+        <v>0.99394608676289198</v>
       </c>
       <c r="AC52">
         <v>5</v>
       </c>
       <c r="AD52" s="1">
-        <v>6.0738731148278705E-8</v>
+        <v>9.10293898931728E-8</v>
       </c>
       <c r="AE52">
-        <v>0.99195749227207397</v>
+        <v>0.99535431121926898</v>
       </c>
       <c r="AF52">
         <v>5</v>
       </c>
       <c r="AG52" s="1">
+        <v>7.6274037538438503E-8</v>
+      </c>
+      <c r="AH52">
+        <v>0.95961848311116504</v>
+      </c>
+      <c r="AI52">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="1">
+        <v>6.0738731148278705E-8</v>
+      </c>
+      <c r="AK52">
+        <v>0.99195749227207397</v>
+      </c>
+      <c r="AL52">
+        <v>5</v>
+      </c>
+      <c r="AM52" s="1">
         <v>7.6437891292282404E-8</v>
       </c>
-      <c r="AH52">
+      <c r="AN52">
         <v>0.98957678192105403</v>
       </c>
     </row>
-    <row r="53" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D53">
         <v>6</v>
       </c>
@@ -26754,53 +28047,71 @@
       <c r="R53" s="1">
         <v>0.99687849768480097</v>
       </c>
-      <c r="T53">
+      <c r="S53" s="1">
         <v>6</v>
       </c>
+      <c r="T53" s="1">
+        <v>4.53188942617046E-7</v>
+      </c>
       <c r="U53" s="1">
-        <v>7.7825911062776596E-8</v>
-      </c>
-      <c r="V53">
-        <v>0.98354668002205303</v>
-      </c>
-      <c r="W53">
+        <v>0.992579207860941</v>
+      </c>
+      <c r="V53" s="1">
         <v>6</v>
       </c>
+      <c r="W53" s="1">
+        <v>8.5506565810324201E-7</v>
+      </c>
       <c r="X53" s="1">
-        <v>7.7500250881271798E-8</v>
-      </c>
-      <c r="Y53">
-        <v>0.99278308622731404</v>
+        <v>0.99927021767180202</v>
       </c>
       <c r="Z53">
         <v>6</v>
       </c>
       <c r="AA53" s="1">
-        <v>8.6292173014325201E-8</v>
+        <v>7.7825911062776596E-8</v>
       </c>
       <c r="AB53">
-        <v>0.98451832131574302</v>
+        <v>0.98354668002205303</v>
       </c>
       <c r="AC53">
         <v>6</v>
       </c>
       <c r="AD53" s="1">
-        <v>7.5886587384684494E-8</v>
+        <v>7.7500250881271798E-8</v>
       </c>
       <c r="AE53">
-        <v>0.99134815976526502</v>
+        <v>0.99278308622731404</v>
       </c>
       <c r="AF53">
         <v>6</v>
       </c>
       <c r="AG53" s="1">
+        <v>8.6292173014325201E-8</v>
+      </c>
+      <c r="AH53">
+        <v>0.98451832131574302</v>
+      </c>
+      <c r="AI53">
+        <v>6</v>
+      </c>
+      <c r="AJ53" s="1">
+        <v>7.5886587384684494E-8</v>
+      </c>
+      <c r="AK53">
+        <v>0.99134815976526502</v>
+      </c>
+      <c r="AL53">
+        <v>6</v>
+      </c>
+      <c r="AM53" s="1">
         <v>3.7660016687917199E-8</v>
       </c>
-      <c r="AH53">
+      <c r="AN53">
         <v>0.86760055191677299</v>
       </c>
     </row>
-    <row r="54" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D54">
         <v>7</v>
       </c>
@@ -26846,53 +28157,71 @@
       <c r="R54" s="3">
         <v>0.99916317419072198</v>
       </c>
-      <c r="T54">
+      <c r="S54" s="3">
         <v>7</v>
       </c>
-      <c r="U54" s="1">
-        <v>9.4786802092552296E-8</v>
-      </c>
-      <c r="V54">
-        <v>0.99773425239721902</v>
-      </c>
-      <c r="W54">
+      <c r="T54" s="3">
+        <v>4.5680909963985598E-7</v>
+      </c>
+      <c r="U54" s="3">
+        <v>0.996463777380451</v>
+      </c>
+      <c r="V54" s="3">
         <v>7</v>
       </c>
-      <c r="X54" s="1">
-        <v>5.4537365634140898E-8</v>
-      </c>
-      <c r="Y54">
-        <v>0.95539606809053601</v>
+      <c r="W54" s="3">
+        <v>7.3354530468187196E-7</v>
+      </c>
+      <c r="X54" s="3">
+        <v>0.99866836610495802</v>
       </c>
       <c r="Z54">
         <v>7</v>
       </c>
       <c r="AA54" s="1">
-        <v>6.6708679081977098E-8</v>
+        <v>9.4786802092552296E-8</v>
       </c>
       <c r="AB54">
-        <v>0.99035687503273095</v>
+        <v>0.99773425239721902</v>
       </c>
       <c r="AC54">
         <v>7</v>
       </c>
       <c r="AD54" s="1">
-        <v>7.6148473419335595E-8</v>
+        <v>5.4537365634140898E-8</v>
       </c>
       <c r="AE54">
-        <v>0.99770513178224696</v>
+        <v>0.95539606809053601</v>
       </c>
       <c r="AF54">
         <v>7</v>
       </c>
       <c r="AG54" s="1">
+        <v>6.6708679081977098E-8</v>
+      </c>
+      <c r="AH54">
+        <v>0.99035687503273095</v>
+      </c>
+      <c r="AI54">
+        <v>7</v>
+      </c>
+      <c r="AJ54" s="1">
+        <v>7.6148473419335595E-8</v>
+      </c>
+      <c r="AK54">
+        <v>0.99770513178224696</v>
+      </c>
+      <c r="AL54">
+        <v>7</v>
+      </c>
+      <c r="AM54" s="1">
         <v>7.3871413747843605E-8</v>
       </c>
-      <c r="AH54">
+      <c r="AN54">
         <v>0.99408409233557504</v>
       </c>
     </row>
-    <row r="55" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D55">
         <v>8</v>
       </c>
@@ -26938,53 +28267,71 @@
       <c r="R55">
         <v>0.99874500804164001</v>
       </c>
-      <c r="T55">
+      <c r="S55">
         <v>8</v>
       </c>
-      <c r="U55" s="1">
-        <v>6.6649929198229796E-8</v>
+      <c r="T55" s="1">
+        <v>4.6504163697478901E-7</v>
+      </c>
+      <c r="U55">
+        <v>0.99402109604571798</v>
       </c>
       <c r="V55">
-        <v>0.98339887509016699</v>
-      </c>
-      <c r="W55">
         <v>8</v>
       </c>
-      <c r="X55" s="1">
-        <v>6.7134188592215001E-8</v>
-      </c>
-      <c r="Y55">
-        <v>0.99524074952218899</v>
+      <c r="W55" s="1">
+        <v>7.8799732533013104E-7</v>
+      </c>
+      <c r="X55">
+        <v>0.99771404807762598</v>
       </c>
       <c r="Z55">
         <v>8</v>
       </c>
       <c r="AA55" s="1">
-        <v>2.3193909120228101E-8</v>
+        <v>6.6649929198229796E-8</v>
       </c>
       <c r="AB55">
-        <v>0.73149336161316902</v>
+        <v>0.98339887509016699</v>
       </c>
       <c r="AC55">
         <v>8</v>
       </c>
       <c r="AD55" s="1">
-        <v>7.2862232063301606E-8</v>
+        <v>6.7134188592215001E-8</v>
       </c>
       <c r="AE55">
-        <v>0.99426211622347005</v>
+        <v>0.99524074952218899</v>
       </c>
       <c r="AF55">
         <v>8</v>
       </c>
       <c r="AG55" s="1">
+        <v>2.3193909120228101E-8</v>
+      </c>
+      <c r="AH55">
+        <v>0.73149336161316902</v>
+      </c>
+      <c r="AI55">
+        <v>8</v>
+      </c>
+      <c r="AJ55" s="1">
+        <v>7.2862232063301606E-8</v>
+      </c>
+      <c r="AK55">
+        <v>0.99426211622347005</v>
+      </c>
+      <c r="AL55">
+        <v>8</v>
+      </c>
+      <c r="AM55" s="1">
         <v>7.7526126333158502E-8</v>
       </c>
-      <c r="AH55">
+      <c r="AN55">
         <v>0.99500523237300098</v>
       </c>
     </row>
-    <row r="56" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D56">
         <v>9</v>
       </c>
@@ -27030,53 +28377,71 @@
       <c r="R56">
         <v>0.99789879453065899</v>
       </c>
-      <c r="T56">
+      <c r="S56">
         <v>9</v>
       </c>
-      <c r="U56" s="1">
-        <v>1.01422787662192E-7</v>
+      <c r="T56" s="1">
+        <v>4.5524975462184898E-7</v>
+      </c>
+      <c r="U56">
+        <v>0.99416293698220104</v>
       </c>
       <c r="V56">
-        <v>0.98520148691909104</v>
-      </c>
-      <c r="W56">
         <v>9</v>
       </c>
-      <c r="X56" s="1">
-        <v>7.9575217700442304E-8</v>
-      </c>
-      <c r="Y56">
-        <v>0.98889010801321897</v>
+      <c r="W56" s="1">
+        <v>8.2088328307322904E-7</v>
+      </c>
+      <c r="X56">
+        <v>0.99922104409742896</v>
       </c>
       <c r="Z56">
         <v>9</v>
       </c>
       <c r="AA56" s="1">
-        <v>5.2705806330158097E-8</v>
+        <v>1.01422787662192E-7</v>
       </c>
       <c r="AB56">
-        <v>0.98151167583705101</v>
+        <v>0.98520148691909104</v>
       </c>
       <c r="AC56">
         <v>9</v>
       </c>
       <c r="AD56" s="1">
-        <v>6.5831859438986096E-8</v>
+        <v>7.9575217700442304E-8</v>
       </c>
       <c r="AE56">
-        <v>0.994023114399464</v>
+        <v>0.98889010801321897</v>
       </c>
       <c r="AF56">
         <v>9</v>
       </c>
       <c r="AG56" s="1">
+        <v>5.2705806330158097E-8</v>
+      </c>
+      <c r="AH56">
+        <v>0.98151167583705101</v>
+      </c>
+      <c r="AI56">
+        <v>9</v>
+      </c>
+      <c r="AJ56" s="1">
+        <v>6.5831859438986096E-8</v>
+      </c>
+      <c r="AK56">
+        <v>0.994023114399464</v>
+      </c>
+      <c r="AL56">
+        <v>9</v>
+      </c>
+      <c r="AM56" s="1">
         <v>7.5663904462611495E-8</v>
       </c>
-      <c r="AH56">
+      <c r="AN56">
         <v>0.93568877898845104</v>
       </c>
     </row>
-    <row r="57" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D57">
         <v>10</v>
       </c>
@@ -27122,53 +28487,71 @@
       <c r="R57">
         <v>0.99929731982558401</v>
       </c>
-      <c r="T57">
+      <c r="S57">
         <v>10</v>
       </c>
-      <c r="U57" s="1">
-        <v>8.8291329595739694E-8</v>
+      <c r="T57" s="1">
+        <v>5.0767983769507804E-7</v>
+      </c>
+      <c r="U57">
+        <v>0.99686746665493497</v>
       </c>
       <c r="V57">
-        <v>0.99814016787944804</v>
-      </c>
-      <c r="W57">
         <v>10</v>
       </c>
-      <c r="X57" s="1">
-        <v>3.8147721195529898E-8</v>
-      </c>
-      <c r="Y57">
-        <v>0.88336347930692005</v>
+      <c r="W57" s="1">
+        <v>8.5041960960384103E-7</v>
+      </c>
+      <c r="X57">
+        <v>0.99912810362015503</v>
       </c>
       <c r="Z57">
         <v>10</v>
       </c>
       <c r="AA57" s="1">
-        <v>5.5441307170179297E-8</v>
+        <v>8.8291329595739694E-8</v>
       </c>
       <c r="AB57">
-        <v>0.97446674917957399</v>
+        <v>0.99814016787944804</v>
       </c>
       <c r="AC57">
         <v>10</v>
       </c>
       <c r="AD57" s="1">
-        <v>5.90938869646742E-8</v>
+        <v>3.8147721195529898E-8</v>
       </c>
       <c r="AE57">
-        <v>0.96005190346690705</v>
+        <v>0.88336347930692005</v>
       </c>
       <c r="AF57">
         <v>10</v>
       </c>
       <c r="AG57" s="1">
+        <v>5.5441307170179297E-8</v>
+      </c>
+      <c r="AH57">
+        <v>0.97446674917957399</v>
+      </c>
+      <c r="AI57">
+        <v>10</v>
+      </c>
+      <c r="AJ57" s="1">
+        <v>5.90938869646742E-8</v>
+      </c>
+      <c r="AK57">
+        <v>0.96005190346690705</v>
+      </c>
+      <c r="AL57">
+        <v>10</v>
+      </c>
+      <c r="AM57" s="1">
         <v>5.8367785007125199E-8</v>
       </c>
-      <c r="AH57">
+      <c r="AN57">
         <v>0.96162792596722502</v>
       </c>
     </row>
-    <row r="58" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D58" t="s">
         <v>21</v>
       </c>
@@ -27214,53 +28597,71 @@
       <c r="R58" s="1">
         <v>4.4559150416986303E-8</v>
       </c>
-      <c r="T58" t="s">
+      <c r="S58" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="T58" s="1">
+        <v>4.6214297704681899E-7</v>
+      </c>
       <c r="U58" s="1">
-        <v>7.5766970436510902E-8</v>
-      </c>
-      <c r="V58" s="1">
-        <v>1.6851421901321501E-8</v>
-      </c>
-      <c r="W58" t="s">
+        <v>3.6669457785559199E-8</v>
+      </c>
+      <c r="V58" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W58" s="1">
+        <v>7.8926903130852297E-7</v>
+      </c>
       <c r="X58" s="1">
-        <v>6.4400101777887004E-8</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>1.53128389893385E-8</v>
+        <v>4.1487908226998501E-8</v>
       </c>
       <c r="Z58" t="s">
         <v>21</v>
       </c>
       <c r="AA58" s="1">
-        <v>6.4093417879696994E-8</v>
+        <v>7.5766970436510902E-8</v>
       </c>
       <c r="AB58" s="1">
-        <v>1.79653425589729E-8</v>
+        <v>1.6851421901321501E-8</v>
       </c>
       <c r="AC58" t="s">
         <v>21</v>
       </c>
       <c r="AD58" s="1">
-        <v>6.6530254183604604E-8</v>
+        <v>6.4400101777887004E-8</v>
       </c>
       <c r="AE58" s="1">
-        <v>1.10475873115709E-8</v>
+        <v>1.53128389893385E-8</v>
       </c>
       <c r="AF58" t="s">
         <v>21</v>
       </c>
       <c r="AG58" s="1">
+        <v>6.4093417879696994E-8</v>
+      </c>
+      <c r="AH58" s="1">
+        <v>1.79653425589729E-8</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ58" s="1">
+        <v>6.6530254183604604E-8</v>
+      </c>
+      <c r="AK58" s="1">
+        <v>1.10475873115709E-8</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM58" s="1">
         <v>6.8396062658816495E-8</v>
       </c>
-      <c r="AH58" s="1">
+      <c r="AN58" s="1">
         <v>1.40398012260563E-8</v>
       </c>
     </row>
-    <row r="59" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:46" x14ac:dyDescent="0.2">
       <c r="F59" s="4">
         <f>F58/E58</f>
         <v>5.2574264455225318E-2</v>
@@ -27281,28 +28682,40 @@
         <f>R58/Q58</f>
         <v>6.8428320433020259E-2</v>
       </c>
-      <c r="V59" s="4">
-        <f>V58/U58</f>
-        <v>0.22241118793897383</v>
-      </c>
-      <c r="Y59" s="4">
-        <f>Y58/X58</f>
-        <v>0.23777662715738834</v>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4">
+        <f>U58/T58</f>
+        <v>7.9346565038992845E-2</v>
+      </c>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4">
+        <f>X58/W58</f>
+        <v>5.2564976682559078E-2</v>
       </c>
       <c r="AB59" s="4">
         <f>AB58/AA58</f>
-        <v>0.28029933733123347</v>
+        <v>0.22241118793897383</v>
       </c>
       <c r="AE59" s="4">
         <f>AE58/AD58</f>
-        <v>0.16605358640420487</v>
+        <v>0.23777662715738834</v>
       </c>
       <c r="AH59" s="4">
         <f>AH58/AG58</f>
+        <v>0.28029933733123347</v>
+      </c>
+      <c r="AK59" s="4">
+        <f>AK58/AJ58</f>
+        <v>0.16605358640420487</v>
+      </c>
+      <c r="AN59" s="4">
+        <f>AN58/AM58</f>
         <v>0.20527206801496373</v>
       </c>
     </row>
-    <row r="61" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>24</v>
       </c>
@@ -27329,31 +28742,49 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" s="1"/>
-      <c r="T61" t="s">
+      <c r="S61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Z61" t="s">
         <v>5</v>
       </c>
-      <c r="U61" s="2"/>
-      <c r="V61" s="2"/>
-      <c r="W61" s="2" t="s">
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2"/>
+      <c r="AC61" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="X61" s="2"/>
-      <c r="Y61" s="2"/>
-      <c r="Z61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC61" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="AD61" s="2"/>
       <c r="AE61" s="2"/>
-      <c r="AF61" s="2" t="s">
+      <c r="AF61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ61" s="2"/>
+      <c r="AK61" s="2"/>
+      <c r="AL61" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG61" s="2"/>
-      <c r="AH61" s="1"/>
+      <c r="AM61" s="2"/>
+      <c r="AN61" s="1"/>
+      <c r="AO61" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP61" s="2"/>
+      <c r="AQ61" s="1"/>
+      <c r="AR61" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="62" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D62">
         <v>1</v>
       </c>
@@ -27399,53 +28830,89 @@
       <c r="R62" s="1">
         <v>0.99604480041880294</v>
       </c>
-      <c r="T62">
+      <c r="S62" s="1">
         <v>1</v>
       </c>
-      <c r="U62" s="2">
+      <c r="T62" s="1">
+        <v>3.1922087058823601E-7</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0.99278818777226496</v>
+      </c>
+      <c r="V62" s="1">
+        <v>1</v>
+      </c>
+      <c r="W62" s="1">
+        <v>4.5316155294117699E-7</v>
+      </c>
+      <c r="X62" s="1">
+        <v>0.99471899354566695</v>
+      </c>
+      <c r="Z62">
+        <v>1</v>
+      </c>
+      <c r="AA62" s="2">
         <v>3.0972704500112499E-8</v>
       </c>
-      <c r="V62" s="2">
+      <c r="AB62" s="2">
         <v>0.97016280601773597</v>
-      </c>
-      <c r="W62" s="2">
-        <v>1</v>
-      </c>
-      <c r="X62" s="2">
-        <v>1.9555951541288501E-8</v>
-      </c>
-      <c r="Y62" s="2">
-        <v>0.92208615359893098</v>
-      </c>
-      <c r="Z62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="1">
-        <v>1.5431614842871099E-8</v>
-      </c>
-      <c r="AB62">
-        <v>0.89887197343228298</v>
       </c>
       <c r="AC62" s="2">
         <v>1</v>
       </c>
       <c r="AD62" s="2">
+        <v>1.9555951541288501E-8</v>
+      </c>
+      <c r="AE62" s="2">
+        <v>0.92208615359893098</v>
+      </c>
+      <c r="AF62" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="1">
+        <v>1.5431614842871099E-8</v>
+      </c>
+      <c r="AH62">
+        <v>0.89887197343228298</v>
+      </c>
+      <c r="AI62" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ62" s="2">
         <v>2.1901519245481099E-8</v>
       </c>
-      <c r="AE62" s="2">
+      <c r="AK62" s="2">
         <v>0.87291174784676195</v>
       </c>
-      <c r="AF62" s="2">
+      <c r="AL62" s="2">
         <v>1</v>
       </c>
-      <c r="AG62" s="2">
+      <c r="AM62" s="2">
         <v>3.4648457218930697E-8</v>
       </c>
-      <c r="AH62" s="1">
+      <c r="AN62" s="1">
         <v>0.97723284020057699</v>
       </c>
+      <c r="AO62">
+        <v>1</v>
+      </c>
+      <c r="AP62" s="1">
+        <v>3.01773430360759E-8</v>
+      </c>
+      <c r="AQ62">
+        <v>0.97762146028188401</v>
+      </c>
+      <c r="AR62">
+        <v>1</v>
+      </c>
+      <c r="AS62" s="1">
+        <v>4.0403889177229399E-8</v>
+      </c>
+      <c r="AT62">
+        <v>0.98884309407731097</v>
+      </c>
     </row>
-    <row r="63" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D63">
         <v>2</v>
       </c>
@@ -27491,53 +28958,89 @@
       <c r="R63" s="1">
         <v>0.98748405735698397</v>
       </c>
-      <c r="T63">
+      <c r="S63" s="1">
         <v>2</v>
       </c>
+      <c r="T63" s="1">
+        <v>3.3508266026410601E-7</v>
+      </c>
       <c r="U63" s="1">
-        <v>3.8363057023925702E-8</v>
-      </c>
-      <c r="V63">
-        <v>0.989170294418664</v>
-      </c>
-      <c r="W63">
+        <v>0.99368809779210199</v>
+      </c>
+      <c r="V63" s="1">
         <v>2</v>
       </c>
+      <c r="W63" s="1">
+        <v>5.2529602112845196E-7</v>
+      </c>
       <c r="X63" s="1">
-        <v>3.3358562409059997E-8</v>
-      </c>
-      <c r="Y63">
-        <v>0.95400274155308395</v>
+        <v>0.99765562694855803</v>
       </c>
       <c r="Z63">
         <v>2</v>
       </c>
       <c r="AA63" s="1">
-        <v>3.1254830353258899E-8</v>
+        <v>3.8363057023925702E-8</v>
       </c>
       <c r="AB63">
-        <v>0.95964302997019602</v>
+        <v>0.989170294418664</v>
       </c>
       <c r="AC63">
         <v>2</v>
       </c>
       <c r="AD63" s="1">
-        <v>3.7971261711542897E-8</v>
+        <v>3.3358562409059997E-8</v>
       </c>
       <c r="AE63">
-        <v>0.99293828802557804</v>
+        <v>0.95400274155308395</v>
       </c>
       <c r="AF63">
         <v>2</v>
       </c>
       <c r="AG63" s="1">
+        <v>3.1254830353258899E-8</v>
+      </c>
+      <c r="AH63">
+        <v>0.95964302997019602</v>
+      </c>
+      <c r="AI63">
+        <v>2</v>
+      </c>
+      <c r="AJ63" s="1">
+        <v>3.7971261711542897E-8</v>
+      </c>
+      <c r="AK63">
+        <v>0.99293828802557804</v>
+      </c>
+      <c r="AL63">
+        <v>2</v>
+      </c>
+      <c r="AM63" s="1">
         <v>4.7484820745518702E-8</v>
       </c>
-      <c r="AH63">
+      <c r="AN63">
         <v>0.99410377591986099</v>
       </c>
+      <c r="AO63">
+        <v>2</v>
+      </c>
+      <c r="AP63" s="1">
+        <v>2.32892346058652E-8</v>
+      </c>
+      <c r="AQ63">
+        <v>0.98419438543806104</v>
+      </c>
+      <c r="AR63">
+        <v>2</v>
+      </c>
+      <c r="AS63" s="1">
+        <v>1.64809255681392E-8</v>
+      </c>
+      <c r="AT63">
+        <v>0.87405141233335104</v>
+      </c>
     </row>
-    <row r="64" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D64">
         <v>3</v>
       </c>
@@ -27583,53 +29086,89 @@
       <c r="R64" s="1">
         <v>0.99747123616163402</v>
       </c>
-      <c r="T64">
+      <c r="S64" s="1">
         <v>3</v>
       </c>
+      <c r="T64" s="1">
+        <v>2.5784448307322901E-7</v>
+      </c>
       <c r="U64" s="1">
-        <v>4.0856594059851602E-8</v>
-      </c>
-      <c r="V64">
-        <v>0.98875052174903499</v>
-      </c>
-      <c r="W64">
+        <v>0.97503493636912897</v>
+      </c>
+      <c r="V64" s="1">
         <v>3</v>
       </c>
+      <c r="W64" s="1">
+        <v>5.35093904441777E-7</v>
+      </c>
       <c r="X64" s="1">
-        <v>3.8768886702167402E-8</v>
-      </c>
-      <c r="Y64">
-        <v>0.98736516341569902</v>
+        <v>0.99834903641436101</v>
       </c>
       <c r="Z64">
         <v>3</v>
       </c>
       <c r="AA64" s="1">
-        <v>3.0778509262732001E-9</v>
+        <v>4.0856594059851602E-8</v>
       </c>
       <c r="AB64">
-        <v>0.72990747150472701</v>
+        <v>0.98875052174903499</v>
       </c>
       <c r="AC64">
         <v>3</v>
       </c>
       <c r="AD64" s="1">
-        <v>2.4908399114977899E-8</v>
+        <v>3.8768886702167402E-8</v>
       </c>
       <c r="AE64">
-        <v>0.96539665345509795</v>
+        <v>0.98736516341569902</v>
       </c>
       <c r="AF64">
         <v>3</v>
       </c>
       <c r="AG64" s="1">
+        <v>3.0778509262732001E-9</v>
+      </c>
+      <c r="AH64">
+        <v>0.72990747150472701</v>
+      </c>
+      <c r="AI64">
+        <v>3</v>
+      </c>
+      <c r="AJ64" s="1">
+        <v>2.4908399114977899E-8</v>
+      </c>
+      <c r="AK64">
+        <v>0.96539665345509795</v>
+      </c>
+      <c r="AL64">
+        <v>3</v>
+      </c>
+      <c r="AM64" s="1">
         <v>1.46564746868671E-8</v>
       </c>
-      <c r="AH64">
+      <c r="AN64">
         <v>0.909491902318323</v>
       </c>
+      <c r="AO64">
+        <v>3</v>
+      </c>
+      <c r="AP64" s="1">
+        <v>8.1908243981099707E-9</v>
+      </c>
+      <c r="AQ64">
+        <v>0.87200801179730802</v>
+      </c>
+      <c r="AR64">
+        <v>3</v>
+      </c>
+      <c r="AS64" s="1">
+        <v>3.0385221600540098E-8</v>
+      </c>
+      <c r="AT64">
+        <v>0.94618076108427396</v>
+      </c>
     </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D65">
         <v>4</v>
       </c>
@@ -27675,53 +29214,89 @@
       <c r="R65" s="1">
         <v>0.99688741054278995</v>
       </c>
-      <c r="T65">
+      <c r="S65" s="1">
         <v>4</v>
       </c>
+      <c r="T65" s="1">
+        <v>2.1838127106842701E-7</v>
+      </c>
       <c r="U65" s="1">
-        <v>1.13517427510688E-8</v>
-      </c>
-      <c r="V65">
-        <v>0.93126826762187198</v>
-      </c>
-      <c r="W65">
+        <v>0.985188806493692</v>
+      </c>
+      <c r="V65" s="1">
         <v>4</v>
       </c>
+      <c r="W65" s="1">
+        <v>5.0026970228091201E-7</v>
+      </c>
       <c r="X65" s="1">
-        <v>1.9968159566489099E-8</v>
-      </c>
-      <c r="Y65">
-        <v>0.90964210210785401</v>
+        <v>0.99791641318157998</v>
       </c>
       <c r="Z65">
         <v>4</v>
       </c>
       <c r="AA65" s="1">
-        <v>2.3317398207455098E-8</v>
+        <v>1.13517427510688E-8</v>
       </c>
       <c r="AB65">
-        <v>0.86750511310508704</v>
+        <v>0.93126826762187198</v>
       </c>
       <c r="AC65">
         <v>4</v>
       </c>
       <c r="AD65" s="1">
-        <v>4.2317420003000001E-8</v>
+        <v>1.9968159566489099E-8</v>
       </c>
       <c r="AE65">
-        <v>0.99582255435494005</v>
+        <v>0.90964210210785401</v>
       </c>
       <c r="AF65">
         <v>4</v>
       </c>
       <c r="AG65" s="1">
+        <v>2.3317398207455098E-8</v>
+      </c>
+      <c r="AH65">
+        <v>0.86750511310508704</v>
+      </c>
+      <c r="AI65">
+        <v>4</v>
+      </c>
+      <c r="AJ65" s="1">
+        <v>4.2317420003000001E-8</v>
+      </c>
+      <c r="AK65">
+        <v>0.99582255435494005</v>
+      </c>
+      <c r="AL65">
+        <v>4</v>
+      </c>
+      <c r="AM65" s="1">
         <v>3.2455668506712503E-8</v>
       </c>
-      <c r="AH65">
+      <c r="AN65">
         <v>0.91971662414800204</v>
       </c>
+      <c r="AO65">
+        <v>4</v>
+      </c>
+      <c r="AP65" s="1">
+        <v>1.7476333015825299E-8</v>
+      </c>
+      <c r="AQ65">
+        <v>0.96182317395178596</v>
+      </c>
+      <c r="AR65">
+        <v>4</v>
+      </c>
+      <c r="AS65" s="1">
+        <v>4.3477679681992198E-8</v>
+      </c>
+      <c r="AT65">
+        <v>0.98931107647182503</v>
+      </c>
     </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D66">
         <v>5</v>
       </c>
@@ -27767,53 +29342,89 @@
       <c r="R66" s="1">
         <v>0.99842072088781597</v>
       </c>
-      <c r="T66">
+      <c r="S66" s="1">
         <v>5</v>
       </c>
+      <c r="T66" s="1">
+        <v>2.3489814752496701E-7</v>
+      </c>
       <c r="U66" s="1">
-        <v>3.0534023783094498E-8</v>
-      </c>
-      <c r="V66">
-        <v>0.97112626076907405</v>
-      </c>
-      <c r="W66">
+        <v>0.99224968393665602</v>
+      </c>
+      <c r="V66" s="1">
         <v>5</v>
       </c>
+      <c r="W66" s="1">
+        <v>5.0712251044417805E-7</v>
+      </c>
       <c r="X66" s="1">
-        <v>2.35672988299708E-8</v>
-      </c>
-      <c r="Y66">
-        <v>0.96214625797686004</v>
+        <v>0.99284886591769905</v>
       </c>
       <c r="Z66">
         <v>5</v>
       </c>
       <c r="AA66" s="1">
-        <v>1.77923226580664E-8</v>
+        <v>3.0534023783094498E-8</v>
       </c>
       <c r="AB66">
-        <v>0.94853294167695001</v>
+        <v>0.97112626076907405</v>
       </c>
       <c r="AC66">
         <v>5</v>
       </c>
       <c r="AD66" s="1">
-        <v>3.1198149463736599E-8</v>
+        <v>2.35672988299708E-8</v>
       </c>
       <c r="AE66">
-        <v>0.98797724943524501</v>
+        <v>0.96214625797686004</v>
       </c>
       <c r="AF66">
         <v>5</v>
       </c>
       <c r="AG66" s="1">
+        <v>1.77923226580664E-8</v>
+      </c>
+      <c r="AH66">
+        <v>0.94853294167695001</v>
+      </c>
+      <c r="AI66">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="1">
+        <v>3.1198149463736599E-8</v>
+      </c>
+      <c r="AK66">
+        <v>0.98797724943524501</v>
+      </c>
+      <c r="AL66">
+        <v>5</v>
+      </c>
+      <c r="AM66" s="1">
         <v>2.57643279006975E-8</v>
       </c>
-      <c r="AH66">
+      <c r="AN66">
         <v>0.95093847809033705</v>
       </c>
+      <c r="AO66">
+        <v>5</v>
+      </c>
+      <c r="AP66" s="1">
+        <v>2.16748549688742E-8</v>
+      </c>
+      <c r="AQ66">
+        <v>0.96786495684127904</v>
+      </c>
+      <c r="AR66">
+        <v>5</v>
+      </c>
+      <c r="AS66" s="1">
+        <v>4.8878590707267699E-8</v>
+      </c>
+      <c r="AT66">
+        <v>0.98950433402004001</v>
+      </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D67">
         <v>6</v>
       </c>
@@ -27859,53 +29470,89 @@
       <c r="R67" s="1">
         <v>0.99677775512675204</v>
       </c>
-      <c r="T67">
+      <c r="S67" s="1">
         <v>6</v>
       </c>
+      <c r="T67" s="1">
+        <v>2.7837153037214902E-7</v>
+      </c>
       <c r="U67" s="1">
-        <v>2.6452799684992101E-8</v>
-      </c>
-      <c r="V67">
-        <v>0.95667575386813197</v>
-      </c>
-      <c r="W67">
+        <v>0.994974713266077</v>
+      </c>
+      <c r="V67" s="1">
         <v>6</v>
       </c>
+      <c r="W67" s="1">
+        <v>5.7235377478991597E-7</v>
+      </c>
       <c r="X67" s="1">
-        <v>2.99738586739668E-8</v>
-      </c>
-      <c r="Y67">
-        <v>0.98430395453742203</v>
+        <v>0.99503109769411202</v>
       </c>
       <c r="Z67">
         <v>6</v>
       </c>
       <c r="AA67" s="1">
-        <v>9.5757700217505292E-9</v>
+        <v>2.6452799684992101E-8</v>
       </c>
       <c r="AB67">
-        <v>0.89717642651450802</v>
+        <v>0.95667575386813197</v>
       </c>
       <c r="AC67">
         <v>6</v>
       </c>
       <c r="AD67" s="1">
-        <v>2.0025560331508299E-8</v>
+        <v>2.99738586739668E-8</v>
       </c>
       <c r="AE67">
-        <v>0.94126855569466705</v>
+        <v>0.98430395453742203</v>
       </c>
       <c r="AF67">
         <v>6</v>
       </c>
       <c r="AG67" s="1">
+        <v>9.5757700217505292E-9</v>
+      </c>
+      <c r="AH67">
+        <v>0.89717642651450802</v>
+      </c>
+      <c r="AI67">
+        <v>6</v>
+      </c>
+      <c r="AJ67" s="1">
+        <v>2.0025560331508299E-8</v>
+      </c>
+      <c r="AK67">
+        <v>0.94126855569466705</v>
+      </c>
+      <c r="AL67">
+        <v>6</v>
+      </c>
+      <c r="AM67" s="1">
         <v>3.0304787474686899E-8</v>
       </c>
-      <c r="AH67">
+      <c r="AN67">
         <v>0.96523729671245095</v>
       </c>
+      <c r="AO67">
+        <v>6</v>
+      </c>
+      <c r="AP67" s="1">
+        <v>2.2807406757668901E-8</v>
+      </c>
+      <c r="AQ67">
+        <v>0.96808276041494601</v>
+      </c>
+      <c r="AR67">
+        <v>6</v>
+      </c>
+      <c r="AS67" s="1">
+        <v>2.7714153146328599E-8</v>
+      </c>
+      <c r="AT67">
+        <v>0.98934070849265099</v>
+      </c>
     </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D68">
         <v>7</v>
       </c>
@@ -27951,53 +29598,89 @@
       <c r="R68" s="3">
         <v>0.99486635312267502</v>
       </c>
-      <c r="T68">
+      <c r="S68" s="3">
         <v>7</v>
       </c>
-      <c r="U68" s="1">
-        <v>2.6759982562063999E-8</v>
-      </c>
-      <c r="V68">
-        <v>0.983943475874271</v>
-      </c>
-      <c r="W68">
+      <c r="T68" s="3">
+        <v>3.0864658199279698E-7</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0.99442317859339502</v>
+      </c>
+      <c r="V68" s="3">
         <v>7</v>
       </c>
-      <c r="X68" s="1">
-        <v>3.3952692784819602E-8</v>
-      </c>
-      <c r="Y68">
-        <v>0.98201262295084901</v>
+      <c r="W68" s="3">
+        <v>5.2847530804321605E-7</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0.99934514551320597</v>
       </c>
       <c r="Z68">
         <v>7</v>
       </c>
       <c r="AA68" s="1">
-        <v>2.6015662371559302E-8</v>
+        <v>2.6759982562063999E-8</v>
       </c>
       <c r="AB68">
-        <v>0.97391412334721195</v>
+        <v>0.983943475874271</v>
       </c>
       <c r="AC68">
         <v>7</v>
       </c>
       <c r="AD68" s="1">
-        <v>3.4760326415660203E-8</v>
+        <v>3.3952692784819602E-8</v>
       </c>
       <c r="AE68">
-        <v>0.96716762516837995</v>
+        <v>0.98201262295084901</v>
       </c>
       <c r="AF68">
         <v>7</v>
       </c>
       <c r="AG68" s="1">
+        <v>2.6015662371559302E-8</v>
+      </c>
+      <c r="AH68">
+        <v>0.97391412334721195</v>
+      </c>
+      <c r="AI68">
+        <v>7</v>
+      </c>
+      <c r="AJ68" s="1">
+        <v>3.4760326415660203E-8</v>
+      </c>
+      <c r="AK68">
+        <v>0.96716762516837995</v>
+      </c>
+      <c r="AL68">
+        <v>7</v>
+      </c>
+      <c r="AM68" s="1">
         <v>2.97305018075453E-8</v>
       </c>
-      <c r="AH68">
+      <c r="AN68">
         <v>0.97502123717843703</v>
       </c>
+      <c r="AO68">
+        <v>7</v>
+      </c>
+      <c r="AP68" s="1">
+        <v>2.9026013199360999E-8</v>
+      </c>
+      <c r="AQ68">
+        <v>0.97903957049729395</v>
+      </c>
+      <c r="AR68">
+        <v>7</v>
+      </c>
+      <c r="AS68" s="1">
+        <v>3.1945957901447598E-8</v>
+      </c>
+      <c r="AT68">
+        <v>0.96716619083445898</v>
+      </c>
     </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D69">
         <v>8</v>
       </c>
@@ -28043,53 +29726,89 @@
       <c r="R69">
         <v>0.99851789833218696</v>
       </c>
-      <c r="T69">
+      <c r="S69">
         <v>8</v>
       </c>
-      <c r="U69" s="1">
-        <v>1.78887068926724E-8</v>
+      <c r="T69" s="1">
+        <v>2.4801574261704702E-7</v>
+      </c>
+      <c r="U69">
+        <v>0.99267700394216396</v>
       </c>
       <c r="V69">
-        <v>0.95944969930642299</v>
-      </c>
-      <c r="W69">
         <v>8</v>
       </c>
-      <c r="X69" s="1">
-        <v>6.0532941048526699E-9</v>
-      </c>
-      <c r="Y69">
-        <v>0.693328550535946</v>
+      <c r="W69" s="1">
+        <v>5.2459847923169296E-7</v>
+      </c>
+      <c r="X69">
+        <v>0.996320115144809</v>
       </c>
       <c r="Z69">
         <v>8</v>
       </c>
       <c r="AA69" s="1">
-        <v>2.2270540696017601E-8</v>
+        <v>1.78887068926724E-8</v>
       </c>
       <c r="AB69">
-        <v>0.91264636348139105</v>
+        <v>0.95944969930642299</v>
       </c>
       <c r="AC69">
         <v>8</v>
       </c>
       <c r="AD69" s="1">
-        <v>2.6918974491862301E-8</v>
+        <v>6.0532941048526699E-9</v>
       </c>
       <c r="AE69">
-        <v>0.98139498762573096</v>
+        <v>0.693328550535946</v>
       </c>
       <c r="AF69">
         <v>8</v>
       </c>
       <c r="AG69" s="1">
+        <v>2.2270540696017601E-8</v>
+      </c>
+      <c r="AH69">
+        <v>0.91264636348139105</v>
+      </c>
+      <c r="AI69">
+        <v>8</v>
+      </c>
+      <c r="AJ69" s="1">
+        <v>2.6918974491862301E-8</v>
+      </c>
+      <c r="AK69">
+        <v>0.98139498762573096</v>
+      </c>
+      <c r="AL69">
+        <v>8</v>
+      </c>
+      <c r="AM69" s="1">
         <v>2.9612325575639401E-8</v>
       </c>
-      <c r="AH69">
+      <c r="AN69">
         <v>0.93412623222586399</v>
       </c>
+      <c r="AO69">
+        <v>8</v>
+      </c>
+      <c r="AP69" s="1">
+        <v>2.7632190107252801E-8</v>
+      </c>
+      <c r="AQ69">
+        <v>0.93958853394580599</v>
+      </c>
+      <c r="AR69">
+        <v>8</v>
+      </c>
+      <c r="AS69" s="1">
+        <v>3.8136478196954799E-8</v>
+      </c>
+      <c r="AT69">
+        <v>0.986381653756641</v>
+      </c>
     </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D70">
         <v>9</v>
       </c>
@@ -28135,53 +29854,89 @@
       <c r="R70">
         <v>0.99711617413337394</v>
       </c>
-      <c r="T70">
+      <c r="S70">
         <v>9</v>
       </c>
-      <c r="U70" s="1">
-        <v>1.8280267674191899E-8</v>
+      <c r="T70" s="1">
+        <v>3.1967627226890802E-7</v>
+      </c>
+      <c r="U70">
+        <v>0.99266774393326196</v>
       </c>
       <c r="V70">
-        <v>0.96367876130713603</v>
-      </c>
-      <c r="W70">
         <v>9</v>
       </c>
-      <c r="X70" s="1">
-        <v>2.7623752036300801E-8</v>
-      </c>
-      <c r="Y70">
-        <v>0.98049909502055799</v>
+      <c r="W70" s="1">
+        <v>5.2544703673469396E-7</v>
+      </c>
+      <c r="X70">
+        <v>0.99406804347402</v>
       </c>
       <c r="Z70">
         <v>9</v>
       </c>
       <c r="AA70" s="1">
-        <v>2.19716130428261E-8</v>
+        <v>1.8280267674191899E-8</v>
       </c>
       <c r="AB70">
-        <v>0.97374192551646699</v>
+        <v>0.96367876130713603</v>
       </c>
       <c r="AC70">
         <v>9</v>
       </c>
       <c r="AD70" s="1">
-        <v>3.0749117017925401E-8</v>
+        <v>2.7623752036300801E-8</v>
       </c>
       <c r="AE70">
-        <v>0.973000572029731</v>
+        <v>0.98049909502055799</v>
       </c>
       <c r="AF70">
         <v>9</v>
       </c>
       <c r="AG70" s="1">
+        <v>2.19716130428261E-8</v>
+      </c>
+      <c r="AH70">
+        <v>0.97374192551646699</v>
+      </c>
+      <c r="AI70">
+        <v>9</v>
+      </c>
+      <c r="AJ70" s="1">
+        <v>3.0749117017925401E-8</v>
+      </c>
+      <c r="AK70">
+        <v>0.973000572029731</v>
+      </c>
+      <c r="AL70">
+        <v>9</v>
+      </c>
+      <c r="AM70" s="1">
         <v>2.85657017850447E-8</v>
       </c>
-      <c r="AH70">
+      <c r="AN70">
         <v>0.98679616154300198</v>
       </c>
+      <c r="AO70">
+        <v>9</v>
+      </c>
+      <c r="AP70" s="1">
+        <v>2.3159825920648098E-8</v>
+      </c>
+      <c r="AQ70">
+        <v>0.991084496368697</v>
+      </c>
+      <c r="AR70">
+        <v>9</v>
+      </c>
+      <c r="AS70" s="1">
+        <v>2.4306679021975701E-8</v>
+      </c>
+      <c r="AT70">
+        <v>0.94081587074268902</v>
+      </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D71">
         <v>10</v>
       </c>
@@ -28227,53 +29982,89 @@
       <c r="R71">
         <v>0.99658592094952703</v>
       </c>
-      <c r="T71">
+      <c r="S71">
         <v>10</v>
       </c>
-      <c r="U71" s="1">
-        <v>3.4182924638116001E-8</v>
+      <c r="T71" s="1">
+        <v>9.1783673469387796E-8</v>
+      </c>
+      <c r="U71">
+        <v>0.80142109949257101</v>
       </c>
       <c r="V71">
-        <v>0.979151197737686</v>
-      </c>
-      <c r="W71">
         <v>10</v>
       </c>
-      <c r="X71" s="1">
-        <v>2.8565985052126299E-8</v>
-      </c>
-      <c r="Y71">
-        <v>0.98959852387934799</v>
+      <c r="W71" s="1">
+        <v>5.3756244081632595E-7</v>
+      </c>
+      <c r="X71">
+        <v>0.99810866336844395</v>
       </c>
       <c r="Z71">
         <v>10</v>
       </c>
       <c r="AA71" s="1">
-        <v>3.2133085202130097E-8</v>
+        <v>3.4182924638116001E-8</v>
       </c>
       <c r="AB71">
-        <v>0.99114744560337997</v>
+        <v>0.979151197737686</v>
       </c>
       <c r="AC71">
         <v>10</v>
       </c>
       <c r="AD71" s="1">
-        <v>1.9731911182779502E-8</v>
+        <v>2.8565985052126299E-8</v>
       </c>
       <c r="AE71">
-        <v>0.88711599790264495</v>
+        <v>0.98959852387934799</v>
       </c>
       <c r="AF71">
         <v>10</v>
       </c>
       <c r="AG71" s="1">
+        <v>3.2133085202130097E-8</v>
+      </c>
+      <c r="AH71">
+        <v>0.99114744560337997</v>
+      </c>
+      <c r="AI71">
+        <v>10</v>
+      </c>
+      <c r="AJ71" s="1">
+        <v>1.9731911182779502E-8</v>
+      </c>
+      <c r="AK71">
+        <v>0.88711599790264495</v>
+      </c>
+      <c r="AL71">
+        <v>10</v>
+      </c>
+      <c r="AM71" s="1">
         <v>4.3302984309607803E-8</v>
       </c>
-      <c r="AH71">
+      <c r="AN71">
         <v>0.98449149094304</v>
       </c>
+      <c r="AO71">
+        <v>10</v>
+      </c>
+      <c r="AP71" s="1">
+        <v>3.3109075939398399E-8</v>
+      </c>
+      <c r="AQ71">
+        <v>0.98887324529674203</v>
+      </c>
+      <c r="AR71">
+        <v>10</v>
+      </c>
+      <c r="AS71" s="1">
+        <v>4.0554475736893302E-8</v>
+      </c>
+      <c r="AT71">
+        <v>0.97593421622029797</v>
+      </c>
     </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D72" t="s">
         <v>21</v>
       </c>
@@ -28319,53 +30110,89 @@
       <c r="R72" s="1">
         <v>3.4840140099567503E-8</v>
       </c>
-      <c r="T72" t="s">
+      <c r="S72" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="T72" s="1">
+        <v>2.6119212332392498E-7</v>
+      </c>
       <c r="U72" s="1">
-        <v>2.75642803570089E-8</v>
-      </c>
-      <c r="V72" s="1">
-        <v>9.4403427289617395E-9</v>
-      </c>
-      <c r="W72" t="s">
+        <v>7.1649446869488398E-8</v>
+      </c>
+      <c r="V72" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W72" s="1">
+        <v>5.2093807308523396E-7</v>
+      </c>
       <c r="X72" s="1">
-        <v>2.61388441701042E-8</v>
-      </c>
-      <c r="Y72" s="1">
-        <v>9.3509109904527792E-9</v>
+        <v>3.0626006558657398E-8</v>
       </c>
       <c r="Z72" t="s">
         <v>21</v>
       </c>
       <c r="AA72" s="1">
-        <v>2.0284068832220799E-8</v>
+        <v>2.75642803570089E-8</v>
       </c>
       <c r="AB72" s="1">
-        <v>9.1291939011890002E-9</v>
+        <v>9.4403427289617395E-9</v>
       </c>
       <c r="AC72" t="s">
         <v>21</v>
       </c>
       <c r="AD72" s="1">
-        <v>2.9048263897847401E-8</v>
+        <v>2.61388441701042E-8</v>
       </c>
       <c r="AE72" s="1">
-        <v>7.7228728225146104E-9</v>
+        <v>9.3509109904527792E-9</v>
       </c>
       <c r="AF72" t="s">
         <v>21</v>
       </c>
       <c r="AG72" s="1">
+        <v>2.0284068832220799E-8</v>
+      </c>
+      <c r="AH72" s="1">
+        <v>9.1291939011890002E-9</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ72" s="1">
+        <v>2.9048263897847401E-8</v>
+      </c>
+      <c r="AK72" s="1">
+        <v>7.7228728225146104E-9</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM72" s="1">
         <v>3.16526050011251E-8</v>
       </c>
-      <c r="AH72" s="1">
+      <c r="AN72" s="1">
         <v>9.0600066970480193E-9</v>
       </c>
+      <c r="AO72" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP72" s="1">
+        <v>2.3654310194907999E-8</v>
+      </c>
+      <c r="AQ72" s="1">
+        <v>7.1408165796306901E-9</v>
+      </c>
+      <c r="AR72" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS72" s="1">
+        <v>3.4228405073876897E-8</v>
+      </c>
+      <c r="AT72" s="1">
+        <v>9.8287255220178092E-9</v>
+      </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:46" x14ac:dyDescent="0.2">
       <c r="F73" s="4">
         <f>F72/E72</f>
         <v>9.7814468930672818E-2</v>
@@ -28386,28 +30213,48 @@
         <f>R72/Q72</f>
         <v>8.2147637424202974E-2</v>
       </c>
-      <c r="V73" s="4">
-        <f>V72/U72</f>
-        <v>0.34248464341138873</v>
-      </c>
-      <c r="Y73" s="4">
-        <f>Y72/X72</f>
-        <v>0.35774003355311723</v>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+      <c r="U73" s="4">
+        <f>U72/T72</f>
+        <v>0.27431702747264802</v>
+      </c>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4">
+        <f>X72/W72</f>
+        <v>5.8790109882497464E-2</v>
       </c>
       <c r="AB73" s="4">
         <f>AB72/AA72</f>
-        <v>0.45006719197715772</v>
+        <v>0.34248464341138873</v>
       </c>
       <c r="AE73" s="4">
         <f>AE72/AD72</f>
-        <v>0.26586349014430799</v>
+        <v>0.35774003355311723</v>
       </c>
       <c r="AH73" s="4">
         <f>AH72/AG72</f>
+        <v>0.45006719197715772</v>
+      </c>
+      <c r="AK73" s="4">
+        <f>AK72/AJ72</f>
+        <v>0.26586349014430799</v>
+      </c>
+      <c r="AN73" s="4">
+        <f>AN72/AM72</f>
         <v>0.28623257696249577</v>
       </c>
+      <c r="AQ73" s="4">
+        <f>AQ72/AP72</f>
+        <v>0.30188225827730436</v>
+      </c>
+      <c r="AT73" s="4">
+        <f>AT72/AS72</f>
+        <v>0.28715113955219279</v>
+      </c>
     </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:46" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>23</v>
       </c>
@@ -28434,31 +30281,49 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" s="1"/>
-      <c r="T75" t="s">
+      <c r="S75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T75" s="2"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Z75" t="s">
         <v>5</v>
       </c>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2" t="s">
+      <c r="AA75" s="2"/>
+      <c r="AB75" s="2"/>
+      <c r="AC75" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-      <c r="Z75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC75" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="AD75" s="2"/>
       <c r="AE75" s="2"/>
-      <c r="AF75" s="2" t="s">
+      <c r="AF75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ75" s="2"/>
+      <c r="AK75" s="2"/>
+      <c r="AL75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG75" s="2"/>
-      <c r="AH75" s="1"/>
+      <c r="AM75" s="2"/>
+      <c r="AN75" s="1"/>
+      <c r="AO75" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AP75" s="2"/>
+      <c r="AQ75" s="1"/>
+      <c r="AR75" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D76">
         <v>1</v>
       </c>
@@ -28504,53 +30369,89 @@
       <c r="R76" s="2">
         <v>0.99076913538578004</v>
       </c>
-      <c r="T76">
+      <c r="S76" s="2">
         <v>1</v>
       </c>
+      <c r="T76" s="2">
+        <v>1.73623134213685E-7</v>
+      </c>
       <c r="U76" s="2">
+        <v>0.99547239423163103</v>
+      </c>
+      <c r="V76" s="2">
+        <v>1</v>
+      </c>
+      <c r="W76" s="2">
+        <v>3.4139055174069601E-7</v>
+      </c>
+      <c r="X76" s="2">
+        <v>0.99625243651608597</v>
+      </c>
+      <c r="Z76">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="2">
         <v>1.46029718367959E-8</v>
       </c>
-      <c r="V76" s="2">
+      <c r="AB76" s="2">
         <v>0.93947961770859101</v>
-      </c>
-      <c r="W76" s="2">
-        <v>1</v>
-      </c>
-      <c r="X76" s="2">
-        <v>6.3582099752494199E-9</v>
-      </c>
-      <c r="Y76" s="2">
-        <v>0.79243168821979304</v>
-      </c>
-      <c r="Z76" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA76" s="1">
-        <v>9.6344648841221008E-9</v>
-      </c>
-      <c r="AB76">
-        <v>0.94270482165724701</v>
       </c>
       <c r="AC76" s="2">
         <v>1</v>
       </c>
       <c r="AD76" s="2">
+        <v>6.3582099752494199E-9</v>
+      </c>
+      <c r="AE76" s="2">
+        <v>0.79243168821979304</v>
+      </c>
+      <c r="AF76" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="1">
+        <v>9.6344648841221008E-9</v>
+      </c>
+      <c r="AH76">
+        <v>0.94270482165724701</v>
+      </c>
+      <c r="AI76" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ76" s="2">
         <v>1.57320083252081E-8</v>
       </c>
-      <c r="AE76" s="2">
+      <c r="AK76" s="2">
         <v>0.98557446392080605</v>
       </c>
-      <c r="AF76" s="2">
+      <c r="AL76" s="2">
         <v>1</v>
       </c>
-      <c r="AG76" s="2">
+      <c r="AM76" s="2">
         <v>6.54399201230034E-9</v>
       </c>
-      <c r="AH76" s="1">
+      <c r="AN76" s="1">
         <v>0.93810185054607098</v>
       </c>
+      <c r="AO76">
+        <v>1</v>
+      </c>
+      <c r="AP76" s="1">
+        <v>1.14869103952598E-8</v>
+      </c>
+      <c r="AQ76">
+        <v>0.95261059366331102</v>
+      </c>
+      <c r="AR76">
+        <v>1</v>
+      </c>
+      <c r="AS76" s="1">
+        <v>1.01226907447687E-8</v>
+      </c>
+      <c r="AT76">
+        <v>0.95183742236542102</v>
+      </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D77">
         <v>2</v>
       </c>
@@ -28596,53 +30497,89 @@
       <c r="R77" s="2">
         <v>0.99427822057752302</v>
       </c>
-      <c r="T77">
+      <c r="S77" s="2">
         <v>2</v>
       </c>
-      <c r="U77" s="1">
-        <v>7.4608232280807003E-9</v>
-      </c>
-      <c r="V77">
-        <v>0.90446625464407904</v>
-      </c>
-      <c r="W77">
+      <c r="T77" s="2">
+        <v>1.6059431116446601E-7</v>
+      </c>
+      <c r="U77" s="2">
+        <v>0.99425052199904895</v>
+      </c>
+      <c r="V77" s="2">
         <v>2</v>
       </c>
-      <c r="X77" s="1">
-        <v>1.01327592739818E-8</v>
-      </c>
-      <c r="Y77">
-        <v>0.956884525118328</v>
+      <c r="W77" s="2">
+        <v>3.2913574309723902E-7</v>
+      </c>
+      <c r="X77" s="2">
+        <v>0.98921099752210995</v>
       </c>
       <c r="Z77">
         <v>2</v>
       </c>
       <c r="AA77" s="1">
-        <v>1.22375778894472E-8</v>
+        <v>7.4608232280807003E-9</v>
       </c>
       <c r="AB77">
-        <v>0.96680619356356101</v>
+        <v>0.90446625464407904</v>
       </c>
       <c r="AC77">
         <v>2</v>
       </c>
       <c r="AD77" s="1">
-        <v>2.16177825395635E-8</v>
+        <v>1.01327592739818E-8</v>
       </c>
       <c r="AE77">
-        <v>0.98192364027148604</v>
+        <v>0.956884525118328</v>
       </c>
       <c r="AF77">
         <v>2</v>
       </c>
       <c r="AG77" s="1">
+        <v>1.22375778894472E-8</v>
+      </c>
+      <c r="AH77">
+        <v>0.96680619356356101</v>
+      </c>
+      <c r="AI77">
+        <v>2</v>
+      </c>
+      <c r="AJ77" s="1">
+        <v>2.16177825395635E-8</v>
+      </c>
+      <c r="AK77">
+        <v>0.98192364027148604</v>
+      </c>
+      <c r="AL77">
+        <v>2</v>
+      </c>
+      <c r="AM77" s="1">
         <v>1.01998400435011E-8</v>
       </c>
-      <c r="AH77">
+      <c r="AN77">
         <v>0.85708633818407598</v>
       </c>
+      <c r="AO77">
+        <v>2</v>
+      </c>
+      <c r="AP77" s="1">
+        <v>1.2645306225155701E-8</v>
+      </c>
+      <c r="AQ77">
+        <v>0.95798489681866295</v>
+      </c>
+      <c r="AR77">
+        <v>2</v>
+      </c>
+      <c r="AS77" s="1">
+        <v>8.9756190729767801E-9</v>
+      </c>
+      <c r="AT77">
+        <v>0.82251648964514301</v>
+      </c>
     </row>
-    <row r="78" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D78">
         <v>3</v>
       </c>
@@ -28688,53 +30625,89 @@
       <c r="R78" s="2">
         <v>0.98870727896444799</v>
       </c>
-      <c r="T78">
+      <c r="S78" s="2">
         <v>3</v>
       </c>
-      <c r="U78" s="1">
-        <v>1.0399681032025799E-8</v>
-      </c>
-      <c r="V78">
-        <v>0.97695723262990897</v>
-      </c>
-      <c r="W78">
+      <c r="T78" s="2">
+        <v>2.1777825546218499E-7</v>
+      </c>
+      <c r="U78" s="2">
+        <v>0.99349603790679197</v>
+      </c>
+      <c r="V78" s="2">
         <v>3</v>
       </c>
-      <c r="X78" s="1">
-        <v>1.15910646441161E-8</v>
-      </c>
-      <c r="Y78">
-        <v>0.94496854409109499</v>
+      <c r="W78" s="2">
+        <v>3.8596178727491002E-7</v>
+      </c>
+      <c r="X78" s="2">
+        <v>0.99825707746527004</v>
       </c>
       <c r="Z78">
         <v>3</v>
       </c>
       <c r="AA78" s="1">
-        <v>1.2580773756843901E-8</v>
+        <v>1.0399681032025799E-8</v>
       </c>
       <c r="AB78">
-        <v>0.91265805843331704</v>
+        <v>0.97695723262990897</v>
       </c>
       <c r="AC78">
         <v>3</v>
       </c>
       <c r="AD78" s="1">
-        <v>1.32297188629715E-8</v>
+        <v>1.15910646441161E-8</v>
       </c>
       <c r="AE78">
-        <v>0.90291508618382699</v>
+        <v>0.94496854409109499</v>
       </c>
       <c r="AF78">
         <v>3</v>
       </c>
       <c r="AG78" s="1">
+        <v>1.2580773756843901E-8</v>
+      </c>
+      <c r="AH78">
+        <v>0.91265805843331704</v>
+      </c>
+      <c r="AI78">
+        <v>3</v>
+      </c>
+      <c r="AJ78" s="1">
+        <v>1.32297188629715E-8</v>
+      </c>
+      <c r="AK78">
+        <v>0.90291508618382699</v>
+      </c>
+      <c r="AL78">
+        <v>3</v>
+      </c>
+      <c r="AM78" s="1">
         <v>7.20108245706143E-9</v>
       </c>
-      <c r="AH78">
+      <c r="AN78">
         <v>0.93273953332718995</v>
       </c>
+      <c r="AO78">
+        <v>3</v>
+      </c>
+      <c r="AP78" s="1">
+        <v>7.3283128478212104E-9</v>
+      </c>
+      <c r="AQ78">
+        <v>0.91762055326665903</v>
+      </c>
+      <c r="AR78">
+        <v>3</v>
+      </c>
+      <c r="AS78" s="1">
+        <v>5.0480148053701199E-9</v>
+      </c>
+      <c r="AT78">
+        <v>0.86209766498696005</v>
+      </c>
     </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D79">
         <v>4</v>
       </c>
@@ -28780,53 +30753,89 @@
       <c r="R79" s="2">
         <v>0.99658177284281302</v>
       </c>
-      <c r="T79">
+      <c r="S79" s="2">
         <v>4</v>
       </c>
-      <c r="U79" s="1">
-        <v>5.8671829145728198E-9</v>
-      </c>
-      <c r="V79">
-        <v>0.79521787132563204</v>
-      </c>
-      <c r="W79">
+      <c r="T79" s="2">
+        <v>2.02990776470588E-7</v>
+      </c>
+      <c r="U79" s="2">
+        <v>0.97190719733695996</v>
+      </c>
+      <c r="V79" s="2">
         <v>4</v>
       </c>
-      <c r="X79" s="1">
-        <v>1.4587752793820201E-9</v>
-      </c>
-      <c r="Y79">
-        <v>0.63609292069985002</v>
+      <c r="W79" s="2">
+        <v>3.3815455894357698E-7</v>
+      </c>
+      <c r="X79" s="2">
+        <v>0.99750558382114896</v>
       </c>
       <c r="Z79">
         <v>4</v>
       </c>
       <c r="AA79" s="1">
-        <v>7.4410946673667196E-9</v>
+        <v>5.8671829145728198E-9</v>
       </c>
       <c r="AB79">
-        <v>0.91689162552516701</v>
+        <v>0.79521787132563204</v>
       </c>
       <c r="AC79">
         <v>4</v>
       </c>
       <c r="AD79" s="1">
-        <v>1.0229594892372301E-8</v>
+        <v>1.4587752793820201E-9</v>
       </c>
       <c r="AE79">
-        <v>0.90096238775804705</v>
+        <v>0.63609292069985002</v>
       </c>
       <c r="AF79">
         <v>4</v>
       </c>
       <c r="AG79" s="1">
+        <v>7.4410946673667196E-9</v>
+      </c>
+      <c r="AH79">
+        <v>0.91689162552516701</v>
+      </c>
+      <c r="AI79">
+        <v>4</v>
+      </c>
+      <c r="AJ79" s="1">
+        <v>1.0229594892372301E-8</v>
+      </c>
+      <c r="AK79">
+        <v>0.90096238775804705</v>
+      </c>
+      <c r="AL79">
+        <v>4</v>
+      </c>
+      <c r="AM79" s="1">
         <v>3.18988509712745E-9</v>
       </c>
-      <c r="AH79">
+      <c r="AN79">
         <v>0.73714613558794695</v>
       </c>
+      <c r="AO79">
+        <v>4</v>
+      </c>
+      <c r="AP79" s="1">
+        <v>3.3385839945999101E-9</v>
+      </c>
+      <c r="AQ79">
+        <v>0.71176559726067101</v>
+      </c>
+      <c r="AR79">
+        <v>4</v>
+      </c>
+      <c r="AS79" s="1">
+        <v>4.4573840096000799E-10</v>
+      </c>
+      <c r="AT79">
+        <v>0.140966574953967</v>
+      </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:46" x14ac:dyDescent="0.2">
       <c r="D80">
         <v>5</v>
       </c>
@@ -28872,53 +30881,89 @@
       <c r="R80" s="2">
         <v>0.99647970636841399</v>
       </c>
-      <c r="T80">
+      <c r="S80" s="2">
         <v>5</v>
       </c>
-      <c r="U80" s="1">
-        <v>5.8848655516388297E-9</v>
-      </c>
-      <c r="V80">
-        <v>0.88172755035893902</v>
-      </c>
-      <c r="W80">
+      <c r="T80" s="2">
+        <v>2.01015893397359E-7</v>
+      </c>
+      <c r="U80" s="2">
+        <v>0.97770062159980498</v>
+      </c>
+      <c r="V80" s="2">
         <v>5</v>
       </c>
-      <c r="X80" s="1">
-        <v>5.31312044551107E-9</v>
-      </c>
-      <c r="Y80">
-        <v>0.83775027294247095</v>
+      <c r="W80" s="2">
+        <v>3.6443559663865502E-7</v>
+      </c>
+      <c r="X80" s="2">
+        <v>0.99326951466966196</v>
       </c>
       <c r="Z80">
         <v>5</v>
       </c>
       <c r="AA80" s="1">
-        <v>1.7939717827945701E-8</v>
+        <v>5.8848655516388297E-9</v>
       </c>
       <c r="AB80">
-        <v>0.97847775839246898</v>
+        <v>0.88172755035893902</v>
       </c>
       <c r="AC80">
         <v>5</v>
       </c>
       <c r="AD80" s="1">
-        <v>2.6967733818345999E-9</v>
+        <v>5.31312044551107E-9</v>
       </c>
       <c r="AE80">
-        <v>0.71143329055395399</v>
+        <v>0.83775027294247095</v>
       </c>
       <c r="AF80">
         <v>5</v>
       </c>
       <c r="AG80" s="1">
+        <v>1.7939717827945701E-8</v>
+      </c>
+      <c r="AH80">
+        <v>0.97847775839246898</v>
+      </c>
+      <c r="AI80">
+        <v>5</v>
+      </c>
+      <c r="AJ80" s="1">
+        <v>2.6967733818345999E-9</v>
+      </c>
+      <c r="AK80">
+        <v>0.71143329055395399</v>
+      </c>
+      <c r="AL80">
+        <v>5</v>
+      </c>
+      <c r="AM80" s="1">
         <v>6.9581184204604802E-9</v>
       </c>
-      <c r="AH80">
+      <c r="AN80">
         <v>0.88784144221585803</v>
       </c>
+      <c r="AO80">
+        <v>5</v>
+      </c>
+      <c r="AP80" s="1">
+        <v>1.20102056176404E-8</v>
+      </c>
+      <c r="AQ80">
+        <v>0.92193082255673697</v>
+      </c>
+      <c r="AR80">
+        <v>5</v>
+      </c>
+      <c r="AS80" s="1">
+        <v>1.4806520108002799E-8</v>
+      </c>
+      <c r="AT80">
+        <v>0.94634579553564302</v>
+      </c>
     </row>
-    <row r="81" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D81">
         <v>6</v>
       </c>
@@ -28964,53 +31009,89 @@
       <c r="R81" s="1">
         <v>0.99711297926638298</v>
       </c>
-      <c r="T81">
+      <c r="S81" s="1">
         <v>6</v>
       </c>
+      <c r="T81" s="1">
+        <v>1.52455808883553E-7</v>
+      </c>
       <c r="U81" s="1">
-        <v>1.20286063151578E-8</v>
-      </c>
-      <c r="V81">
-        <v>0.961244219811205</v>
-      </c>
-      <c r="W81">
+        <v>0.96331310263888004</v>
+      </c>
+      <c r="V81" s="1">
         <v>6</v>
       </c>
+      <c r="W81" s="1">
+        <v>3.7382644561824699E-7</v>
+      </c>
       <c r="X81" s="1">
-        <v>7.20196115652889E-9</v>
-      </c>
-      <c r="Y81">
-        <v>0.89995590827504401</v>
+        <v>0.99611709869406795</v>
       </c>
       <c r="Z81">
         <v>6</v>
       </c>
       <c r="AA81" s="1">
-        <v>1.19903487887197E-8</v>
+        <v>1.20286063151578E-8</v>
       </c>
       <c r="AB81">
-        <v>0.95270497751405103</v>
+        <v>0.961244219811205</v>
       </c>
       <c r="AC81">
         <v>6</v>
       </c>
       <c r="AD81" s="1">
-        <v>7.6297140403509995E-9</v>
+        <v>7.20196115652889E-9</v>
       </c>
       <c r="AE81">
-        <v>0.940198566597786</v>
+        <v>0.89995590827504401</v>
       </c>
       <c r="AF81">
         <v>6</v>
       </c>
       <c r="AG81" s="1">
+        <v>1.19903487887197E-8</v>
+      </c>
+      <c r="AH81">
+        <v>0.95270497751405103</v>
+      </c>
+      <c r="AI81">
+        <v>6</v>
+      </c>
+      <c r="AJ81" s="1">
+        <v>7.6297140403509995E-9</v>
+      </c>
+      <c r="AK81">
+        <v>0.940198566597786</v>
+      </c>
+      <c r="AL81">
+        <v>6</v>
+      </c>
+      <c r="AM81" s="1">
         <v>4.1425549688741802E-9</v>
       </c>
-      <c r="AH81">
+      <c r="AN81">
         <v>0.92188991166577094</v>
       </c>
+      <c r="AO81">
+        <v>6</v>
+      </c>
+      <c r="AP81" s="1">
+        <v>4.3274185779643799E-9</v>
+      </c>
+      <c r="AQ81">
+        <v>0.65731270868107905</v>
+      </c>
+      <c r="AR81">
+        <v>6</v>
+      </c>
+      <c r="AS81" s="1">
+        <v>1.6341701207530099E-8</v>
+      </c>
+      <c r="AT81">
+        <v>0.93283155487133596</v>
+      </c>
     </row>
-    <row r="82" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D82">
         <v>7</v>
       </c>
@@ -29056,53 +31137,89 @@
       <c r="R82" s="3">
         <v>0.98461577183583404</v>
       </c>
-      <c r="T82">
+      <c r="S82" s="3">
         <v>7</v>
       </c>
-      <c r="U82" s="1">
-        <v>1.10845580589514E-8</v>
-      </c>
-      <c r="V82">
-        <v>0.90307468039066596</v>
-      </c>
-      <c r="W82">
+      <c r="T82" s="3">
+        <v>1.4317108427371001E-7</v>
+      </c>
+      <c r="U82" s="3">
+        <v>0.99282540152054899</v>
+      </c>
+      <c r="V82" s="3">
         <v>7</v>
       </c>
-      <c r="X82" s="1">
-        <v>4.3585397059926696E-9</v>
-      </c>
-      <c r="Y82">
-        <v>0.85164940305199099</v>
+      <c r="W82" s="3">
+        <v>2.8837118799519801E-7</v>
+      </c>
+      <c r="X82" s="3">
+        <v>0.987641049362882</v>
       </c>
       <c r="Z82">
         <v>7</v>
       </c>
       <c r="AA82" s="1">
-        <v>1.03106152253806E-8</v>
+        <v>1.10845580589514E-8</v>
       </c>
       <c r="AB82">
-        <v>0.79992626671749401</v>
+        <v>0.90307468039066596</v>
       </c>
       <c r="AC82">
         <v>7</v>
       </c>
       <c r="AD82" s="1">
-        <v>4.4322503337582598E-9</v>
+        <v>4.3585397059926696E-9</v>
       </c>
       <c r="AE82">
-        <v>0.56790911009764</v>
+        <v>0.85164940305199099</v>
       </c>
       <c r="AF82">
         <v>7</v>
       </c>
       <c r="AG82" s="1">
+        <v>1.03106152253806E-8</v>
+      </c>
+      <c r="AH82">
+        <v>0.79992626671749401</v>
+      </c>
+      <c r="AI82">
+        <v>7</v>
+      </c>
+      <c r="AJ82" s="1">
+        <v>4.4322503337582598E-9</v>
+      </c>
+      <c r="AK82">
+        <v>0.56790911009764</v>
+      </c>
+      <c r="AL82">
+        <v>7</v>
+      </c>
+      <c r="AM82" s="1">
         <v>1.3671111062776601E-8</v>
       </c>
-      <c r="AH82">
+      <c r="AN82">
         <v>0.94916030171760102</v>
       </c>
+      <c r="AO82">
+        <v>7</v>
+      </c>
+      <c r="AP82" s="1">
+        <v>8.6511445086705508E-9</v>
+      </c>
+      <c r="AQ82">
+        <v>0.84682250093838296</v>
+      </c>
+      <c r="AR82">
+        <v>7</v>
+      </c>
+      <c r="AS82" s="1">
+        <v>3.5315434335858099E-9</v>
+      </c>
+      <c r="AT82">
+        <v>0.80487219616999195</v>
+      </c>
     </row>
-    <row r="83" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D83">
         <v>8</v>
       </c>
@@ -29148,53 +31265,89 @@
       <c r="R83">
         <v>0.99572541311112395</v>
       </c>
-      <c r="T83">
+      <c r="S83">
         <v>8</v>
       </c>
-      <c r="U83" s="1">
-        <v>5.6076041326033098E-9</v>
+      <c r="T83" s="1">
+        <v>1.2984315582232901E-7</v>
+      </c>
+      <c r="U83">
+        <v>0.95906167243394302</v>
       </c>
       <c r="V83">
-        <v>0.87879386134703397</v>
-      </c>
-      <c r="W83">
         <v>8</v>
       </c>
-      <c r="X83" s="1">
-        <v>3.2168948098703098E-9</v>
-      </c>
-      <c r="Y83">
-        <v>0.70940275457400104</v>
+      <c r="W83" s="1">
+        <v>3.1250770804321698E-7</v>
+      </c>
+      <c r="X83">
+        <v>0.99538688998926805</v>
       </c>
       <c r="Z83">
         <v>8</v>
       </c>
       <c r="AA83" s="1">
-        <v>9.5835669016725204E-9</v>
+        <v>5.6076041326033098E-9</v>
       </c>
       <c r="AB83">
-        <v>0.93479941689511903</v>
+        <v>0.87879386134703397</v>
       </c>
       <c r="AC83">
         <v>8</v>
       </c>
       <c r="AD83" s="1">
-        <v>5.6796393909848102E-9</v>
+        <v>3.2168948098703098E-9</v>
       </c>
       <c r="AE83">
-        <v>0.72192078994759001</v>
+        <v>0.70940275457400104</v>
       </c>
       <c r="AF83">
         <v>8</v>
       </c>
       <c r="AG83" s="1">
+        <v>9.5835669016725204E-9</v>
+      </c>
+      <c r="AH83">
+        <v>0.93479941689511903</v>
+      </c>
+      <c r="AI83">
+        <v>8</v>
+      </c>
+      <c r="AJ83" s="1">
+        <v>5.6796393909848102E-9</v>
+      </c>
+      <c r="AK83">
+        <v>0.72192078994759001</v>
+      </c>
+      <c r="AL83">
+        <v>8</v>
+      </c>
+      <c r="AM83" s="1">
         <v>4.3262284707117003E-9</v>
       </c>
-      <c r="AH83">
+      <c r="AN83">
         <v>0.86749869857516104</v>
       </c>
+      <c r="AO83">
+        <v>8</v>
+      </c>
+      <c r="AP83" s="1">
+        <v>3.5127719567988802E-9</v>
+      </c>
+      <c r="AQ83">
+        <v>0.77242098556168404</v>
+      </c>
+      <c r="AR83">
+        <v>8</v>
+      </c>
+      <c r="AS83" s="1">
+        <v>4.61887677191926E-9</v>
+      </c>
+      <c r="AT83">
+        <v>0.84764663285603403</v>
+      </c>
     </row>
-    <row r="84" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D84">
         <v>9</v>
       </c>
@@ -29240,53 +31393,89 @@
       <c r="R84">
         <v>0.98111290322955702</v>
       </c>
-      <c r="T84">
+      <c r="S84">
         <v>9</v>
       </c>
-      <c r="U84" s="1">
-        <v>1.37653244731117E-8</v>
+      <c r="T84" s="1">
+        <v>1.4048663673469399E-7</v>
+      </c>
+      <c r="U84">
+        <v>0.97753162488286305</v>
       </c>
       <c r="V84">
-        <v>0.96830222710304104</v>
-      </c>
-      <c r="W84">
         <v>9</v>
       </c>
-      <c r="X84" s="1">
-        <v>2.7026050026250598E-9</v>
-      </c>
-      <c r="Y84">
-        <v>0.57832666716132697</v>
+      <c r="W84" s="1">
+        <v>3.4774332244897997E-7</v>
+      </c>
+      <c r="X84">
+        <v>0.99718560197472705</v>
       </c>
       <c r="Z84">
         <v>9</v>
       </c>
       <c r="AA84" s="1">
-        <v>1.9399222500562599E-8</v>
+        <v>1.37653244731117E-8</v>
       </c>
       <c r="AB84">
-        <v>0.97284902595387801</v>
+        <v>0.96830222710304104</v>
       </c>
       <c r="AC84">
         <v>9</v>
       </c>
       <c r="AD84" s="1">
-        <v>1.75312213530339E-8</v>
+        <v>2.7026050026250598E-9</v>
       </c>
       <c r="AE84">
-        <v>0.94708085549252796</v>
+        <v>0.57832666716132697</v>
       </c>
       <c r="AF84">
         <v>9</v>
       </c>
       <c r="AG84" s="1">
+        <v>1.9399222500562599E-8</v>
+      </c>
+      <c r="AH84">
+        <v>0.97284902595387801</v>
+      </c>
+      <c r="AI84">
+        <v>9</v>
+      </c>
+      <c r="AJ84" s="1">
+        <v>1.75312213530339E-8</v>
+      </c>
+      <c r="AK84">
+        <v>0.94708085549252796</v>
+      </c>
+      <c r="AL84">
+        <v>9</v>
+      </c>
+      <c r="AM84" s="1">
         <v>6.1774499587489801E-9</v>
       </c>
-      <c r="AH84">
+      <c r="AN84">
         <v>0.89495678556108205</v>
       </c>
+      <c r="AO84">
+        <v>9</v>
+      </c>
+      <c r="AP84" s="1">
+        <v>1.039376120153E-8</v>
+      </c>
+      <c r="AQ84">
+        <v>0.97484486442590301</v>
+      </c>
+      <c r="AR84">
+        <v>9</v>
+      </c>
+      <c r="AS84" s="1">
+        <v>1.1984164839121E-8</v>
+      </c>
+      <c r="AT84">
+        <v>0.93776555394285399</v>
+      </c>
     </row>
-    <row r="85" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D85">
         <v>10</v>
       </c>
@@ -29332,53 +31521,89 @@
       <c r="R85">
         <v>0.98731503206598104</v>
       </c>
-      <c r="T85">
+      <c r="S85">
         <v>10</v>
       </c>
-      <c r="U85" s="1">
-        <v>3.9259416185404497E-9</v>
+      <c r="T85" s="1">
+        <v>2.10301982713085E-7</v>
+      </c>
+      <c r="U85">
+        <v>0.98198173160681901</v>
       </c>
       <c r="V85">
-        <v>0.88473295493128701</v>
-      </c>
-      <c r="W85">
         <v>10</v>
       </c>
-      <c r="X85" s="1">
-        <v>1.1817154676367E-8</v>
-      </c>
-      <c r="Y85">
-        <v>0.968298537722599</v>
+      <c r="W85" s="1">
+        <v>3.0405443025210099E-7</v>
+      </c>
+      <c r="X85">
+        <v>0.99624612100351595</v>
       </c>
       <c r="Z85">
         <v>10</v>
       </c>
       <c r="AA85" s="1">
-        <v>7.5416730143253196E-9</v>
+        <v>3.9259416185404497E-9</v>
       </c>
       <c r="AB85">
-        <v>0.95678219341295401</v>
+        <v>0.88473295493128701</v>
       </c>
       <c r="AC85">
         <v>10</v>
       </c>
       <c r="AD85" s="1">
-        <v>1.0482991757293999E-8</v>
+        <v>1.1817154676367E-8</v>
       </c>
       <c r="AE85">
-        <v>0.9233920122514</v>
+        <v>0.968298537722599</v>
       </c>
       <c r="AF85">
         <v>10</v>
       </c>
       <c r="AG85" s="1">
+        <v>7.5416730143253196E-9</v>
+      </c>
+      <c r="AH85">
+        <v>0.95678219341295401</v>
+      </c>
+      <c r="AI85">
+        <v>10</v>
+      </c>
+      <c r="AJ85" s="1">
+        <v>1.0482991757293999E-8</v>
+      </c>
+      <c r="AK85">
+        <v>0.9233920122514</v>
+      </c>
+      <c r="AL85">
+        <v>10</v>
+      </c>
+      <c r="AM85" s="1">
         <v>4.0854677941948201E-9</v>
       </c>
-      <c r="AH85">
+      <c r="AN85">
         <v>0.77763658639397004</v>
       </c>
+      <c r="AO85">
+        <v>10</v>
+      </c>
+      <c r="AP85" s="1">
+        <v>6.1761939098477696E-9</v>
+      </c>
+      <c r="AQ85">
+        <v>0.76611665796797601</v>
+      </c>
+      <c r="AR85">
+        <v>10</v>
+      </c>
+      <c r="AS85" s="1">
+        <v>7.8509185179628697E-9</v>
+      </c>
+      <c r="AT85">
+        <v>0.93182730389471602</v>
+      </c>
     </row>
-    <row r="86" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:46" x14ac:dyDescent="0.2">
       <c r="D86" t="s">
         <v>21</v>
       </c>
@@ -29424,53 +31649,89 @@
       <c r="R86" s="1">
         <v>1.67798176544268E-8</v>
       </c>
-      <c r="T86" t="s">
+      <c r="S86" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="T86" s="1">
+        <v>1.73226103913565E-7</v>
+      </c>
       <c r="U86" s="1">
-        <v>9.0627559161478905E-9</v>
-      </c>
-      <c r="V86" s="1">
-        <v>3.7812587855476797E-9</v>
-      </c>
-      <c r="W86" t="s">
+        <v>3.2431303819497297E-8</v>
+      </c>
+      <c r="V86" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="W86" s="1">
+        <v>3.3855813320528202E-7</v>
+      </c>
       <c r="X86" s="1">
-        <v>6.4151084969624403E-9</v>
-      </c>
-      <c r="Y86" s="1">
-        <v>3.7183668998363102E-9</v>
+        <v>3.1144462028171203E-8</v>
       </c>
       <c r="Z86" t="s">
         <v>21</v>
       </c>
       <c r="AA86" s="1">
-        <v>1.18659055456386E-8</v>
+        <v>9.0627559161478905E-9</v>
       </c>
       <c r="AB86" s="1">
-        <v>4.0165212474448301E-9</v>
+        <v>3.7812587855476797E-9</v>
       </c>
       <c r="AC86" t="s">
         <v>21</v>
       </c>
       <c r="AD86" s="1">
-        <v>1.09261694877372E-8</v>
+        <v>6.4151084969624403E-9</v>
       </c>
       <c r="AE86" s="1">
-        <v>6.1038056610954398E-9</v>
+        <v>3.7183668998363102E-9</v>
       </c>
       <c r="AF86" t="s">
         <v>21</v>
       </c>
       <c r="AG86" s="1">
+        <v>1.18659055456386E-8</v>
+      </c>
+      <c r="AH86" s="1">
+        <v>4.0165212474448301E-9</v>
+      </c>
+      <c r="AI86" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ86" s="1">
+        <v>1.09261694877372E-8</v>
+      </c>
+      <c r="AK86" s="1">
+        <v>6.1038056610954398E-9</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM86" s="1">
         <v>6.6495730285757098E-9</v>
       </c>
-      <c r="AH86" s="1">
+      <c r="AN86" s="1">
         <v>3.2105200066488602E-9</v>
       </c>
+      <c r="AO86" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP86" s="1">
+        <v>7.9870609235288698E-9</v>
+      </c>
+      <c r="AQ86" s="1">
+        <v>3.5761691493578401E-9</v>
+      </c>
+      <c r="AR86" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS86" s="1">
+        <v>8.3725787902197404E-9</v>
+      </c>
+      <c r="AT86" s="1">
+        <v>5.0887476309079104E-9</v>
+      </c>
     </row>
-    <row r="87" spans="4:34" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:46" x14ac:dyDescent="0.2">
       <c r="F87" s="4">
         <f>F86/E86</f>
         <v>0.22549294352428537</v>
@@ -29491,25 +31752,45 @@
         <f>R86/Q86</f>
         <v>6.6454777512605215E-2</v>
       </c>
-      <c r="V87" s="4">
-        <f>V86/U86</f>
-        <v>0.41723056656643331</v>
-      </c>
-      <c r="Y87" s="4">
-        <f>Y86/X86</f>
-        <v>0.5796265022792616</v>
+      <c r="S87" s="4"/>
+      <c r="T87" s="4"/>
+      <c r="U87" s="4">
+        <f>U86/T86</f>
+        <v>0.18721949571572433</v>
+      </c>
+      <c r="V87" s="4"/>
+      <c r="W87" s="4"/>
+      <c r="X87" s="4">
+        <f>X86/W86</f>
+        <v>9.1991474944974977E-2</v>
       </c>
       <c r="AB87" s="4">
         <f>AB86/AA86</f>
-        <v>0.33849260235525236</v>
+        <v>0.41723056656643331</v>
       </c>
       <c r="AE87" s="4">
         <f>AE86/AD86</f>
-        <v>0.55864094621138194</v>
+        <v>0.5796265022792616</v>
       </c>
       <c r="AH87" s="4">
         <f>AH86/AG86</f>
+        <v>0.33849260235525236</v>
+      </c>
+      <c r="AK87" s="4">
+        <f>AK86/AJ86</f>
+        <v>0.55864094621138194</v>
+      </c>
+      <c r="AN87" s="4">
+        <f>AN86/AM86</f>
         <v>0.48281596319824616</v>
+      </c>
+      <c r="AQ87" s="4">
+        <f>AQ86/AP86</f>
+        <v>0.44774532003667317</v>
+      </c>
+      <c r="AT87" s="4">
+        <f>AT86/AS86</f>
+        <v>0.60778736855271265</v>
       </c>
     </row>
   </sheetData>
